--- a/InputData/trans/SYFAFE/Start Year Fleet Avg Fuel Economy.xlsx
+++ b/InputData/trans/SYFAFE/Start Year Fleet Avg Fuel Economy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\SYFAFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9630EDC8-0D77-46A6-AA62-272918A1CADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F5A835-7C4F-422F-895B-93B85D852E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37230" yWindow="810" windowWidth="23370" windowHeight="12975" tabRatio="784" firstSheet="9" activeTab="17" xr2:uid="{45C79576-D266-44E4-9E44-3FFC5A94C2AF}"/>
+    <workbookView xWindow="41490" yWindow="2040" windowWidth="26580" windowHeight="11490" tabRatio="784" firstSheet="8" activeTab="18" xr2:uid="{45C79576-D266-44E4-9E44-3FFC5A94C2AF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <externalReference r:id="rId22"/>
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
   </externalReferences>
   <definedNames>
     <definedName name="Eno_TM">'[1]1997  Table 1a Modified'!#REF!</definedName>
@@ -1419,7 +1420,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="15">
+  <numFmts count="16">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1435,6 +1436,7 @@
     <numFmt numFmtId="175" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="#,##0.0"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1957,7 +1959,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2219,6 +2221,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="13">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Body: normal cell" xfId="12" xr:uid="{0A7EBA85-0124-4D78-A8C8-9648650E01A5}"/>
@@ -2719,6 +2722,103 @@
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="DV-psgr"/>
+      <sheetName val="DV-2017regis"/>
+      <sheetName val="DV-freight"/>
+      <sheetName val="BAADTbVT_air"/>
+      <sheetName val="ships-psgr"/>
+      <sheetName val="ships-frgt"/>
+      <sheetName val="subway"/>
+      <sheetName val="고속철도 여객수송동향"/>
+      <sheetName val="열차 여객수송인원"/>
+      <sheetName val="rail"/>
+      <sheetName val="US AVLo"/>
+      <sheetName val="SYAVLo-passengers"/>
+      <sheetName val="SYAVLo-freight"/>
+      <sheetName val="AVLo-passengers"/>
+      <sheetName val="AVLo-freight"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="41">
+          <cell r="H41">
+            <v>1.404094416519162</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="H42">
+            <v>14.731070293267342</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3">
+        <row r="10">
+          <cell r="K10">
+            <v>27.6</v>
+          </cell>
+          <cell r="O10">
+            <v>1.2304866591260886</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="7">
+          <cell r="L7">
+            <v>63.556825639903742</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>155.72981935122084</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10">
+        <row r="15">
+          <cell r="C15">
+            <v>1514.4</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30">
+            <v>382.85954795395736</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="14">
+          <cell r="B14">
+            <v>1974.4736422180429</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
       <sheetName val="SYVbT_passenger"/>
@@ -2750,6 +2850,8 @@
       <sheetName val="Air-Cal"/>
       <sheetName val="Motorbikes"/>
       <sheetName val="Ships-Cal"/>
+      <sheetName val="SYAADTbVT-passengers"/>
+      <sheetName val="SYAADTbVT-freight"/>
       <sheetName val="BAADTbVT-passengers"/>
       <sheetName val="BAADTbVT-freight"/>
       <sheetName val="AVLo-passenger"/>
@@ -2763,36 +2865,36 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5">
         <row r="4">
           <cell r="S4">
-            <v>7645.3386159425945</v>
+            <v>7773.9211010803465</v>
           </cell>
         </row>
         <row r="7">
           <cell r="S7">
-            <v>9323.117790227654</v>
+            <v>9173.2806946391247</v>
           </cell>
         </row>
         <row r="10">
           <cell r="S10">
-            <v>9169.809811392035</v>
+            <v>9145.6217826062839</v>
           </cell>
         </row>
         <row r="13">
           <cell r="S13">
-            <v>18979.686196888564</v>
+            <v>18011.228582969787</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10">
         <row r="6">
           <cell r="G6">
@@ -2805,22 +2907,22 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
       <sheetData sheetId="27">
         <row r="4">
           <cell r="O4">
@@ -2846,29 +2948,29 @@
         </row>
       </sheetData>
       <sheetData sheetId="29">
-        <row r="69">
-          <cell r="H69">
-            <v>10551.03452890655</v>
-          </cell>
-        </row>
         <row r="72">
           <cell r="H72">
             <v>81662.909988119718</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
       <sheetName val="SYVbT_DV-Regis"/>
@@ -2897,24 +2999,303 @@
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
-        <row r="82">
-          <cell r="N82">
-            <v>2.5754463465193611E-2</v>
+        <row r="83">
+          <cell r="N83">
+            <v>-4.4412307467669221E-2</v>
           </cell>
         </row>
-        <row r="83">
-          <cell r="N83">
-            <v>-4.5194730002432681E-2</v>
+        <row r="89">
+          <cell r="E89">
+            <v>65321.41599690765</v>
+          </cell>
+          <cell r="F89">
+            <v>66899.017733983914</v>
+          </cell>
+          <cell r="G89">
+            <v>68476.619471060185</v>
+          </cell>
+          <cell r="H89">
+            <v>70054.221208136456</v>
+          </cell>
+          <cell r="I89">
+            <v>71631.822945212727</v>
+          </cell>
+          <cell r="J89">
+            <v>73209.424682288998</v>
+          </cell>
+          <cell r="K89">
+            <v>74787.026419365269</v>
+          </cell>
+          <cell r="L89">
+            <v>76364.62815644154</v>
+          </cell>
+          <cell r="M89">
+            <v>77942.229893517811</v>
+          </cell>
+          <cell r="N89">
+            <v>79519.831630594083</v>
+          </cell>
+          <cell r="O89">
+            <v>81097.433367670354</v>
+          </cell>
+          <cell r="P89">
+            <v>82675.035104746625</v>
+          </cell>
+          <cell r="Q89">
+            <v>84252.636841822896</v>
+          </cell>
+          <cell r="R89">
+            <v>85830.238578899167</v>
+          </cell>
+          <cell r="S89">
+            <v>87407.840315975438</v>
+          </cell>
+          <cell r="T89">
+            <v>88985.442053051709</v>
+          </cell>
+          <cell r="U89">
+            <v>90563.04379012798</v>
+          </cell>
+          <cell r="V89">
+            <v>92140.645527204251</v>
+          </cell>
+          <cell r="W89">
+            <v>93718.247264280522</v>
+          </cell>
+          <cell r="X89">
+            <v>95295.849001356793</v>
+          </cell>
+          <cell r="Y89">
+            <v>96873.450738433065</v>
+          </cell>
+          <cell r="Z89">
+            <v>98451.052475509336</v>
+          </cell>
+          <cell r="AA89">
+            <v>100028.65421258561</v>
+          </cell>
+          <cell r="AB89">
+            <v>101606.25594966188</v>
+          </cell>
+          <cell r="AC89">
+            <v>103183.85768673815</v>
+          </cell>
+          <cell r="AD89">
+            <v>104761.45942381442</v>
+          </cell>
+          <cell r="AE89">
+            <v>106339.06116089069</v>
+          </cell>
+          <cell r="AF89">
+            <v>107916.66289796696</v>
+          </cell>
+          <cell r="AG89">
+            <v>109494.26463504323</v>
+          </cell>
+          <cell r="AH89">
+            <v>111071.8663721195</v>
+          </cell>
+          <cell r="AI89">
+            <v>112649.46810919578</v>
+          </cell>
+          <cell r="AJ89">
+            <v>114227.06984627205</v>
           </cell>
         </row>
-        <row r="84">
-          <cell r="N84">
-            <v>4.2610726525127429E-3</v>
+        <row r="91">
+          <cell r="E91">
+            <v>14476.508872153761</v>
+          </cell>
+          <cell r="F91">
+            <v>14528.158002277896</v>
+          </cell>
+          <cell r="G91">
+            <v>14579.807132402031</v>
+          </cell>
+          <cell r="H91">
+            <v>14631.456262526166</v>
+          </cell>
+          <cell r="I91">
+            <v>14683.105392650301</v>
+          </cell>
+          <cell r="J91">
+            <v>14734.754522774436</v>
+          </cell>
+          <cell r="K91">
+            <v>14786.403652898571</v>
+          </cell>
+          <cell r="L91">
+            <v>14838.052783022706</v>
+          </cell>
+          <cell r="M91">
+            <v>14889.701913146841</v>
+          </cell>
+          <cell r="N91">
+            <v>14941.351043270975</v>
+          </cell>
+          <cell r="O91">
+            <v>14993.00017339511</v>
+          </cell>
+          <cell r="P91">
+            <v>15044.649303519245</v>
+          </cell>
+          <cell r="Q91">
+            <v>15096.29843364338</v>
+          </cell>
+          <cell r="R91">
+            <v>15147.947563767515</v>
+          </cell>
+          <cell r="S91">
+            <v>15199.59669389165</v>
+          </cell>
+          <cell r="T91">
+            <v>15251.245824015785</v>
+          </cell>
+          <cell r="U91">
+            <v>15302.89495413992</v>
+          </cell>
+          <cell r="V91">
+            <v>15354.544084264055</v>
+          </cell>
+          <cell r="W91">
+            <v>15406.19321438819</v>
+          </cell>
+          <cell r="X91">
+            <v>15457.842344512324</v>
+          </cell>
+          <cell r="Y91">
+            <v>15509.491474636459</v>
+          </cell>
+          <cell r="Z91">
+            <v>15561.140604760594</v>
+          </cell>
+          <cell r="AA91">
+            <v>15612.789734884729</v>
+          </cell>
+          <cell r="AB91">
+            <v>15664.438865008864</v>
+          </cell>
+          <cell r="AC91">
+            <v>15716.087995132999</v>
+          </cell>
+          <cell r="AD91">
+            <v>15767.737125257134</v>
+          </cell>
+          <cell r="AE91">
+            <v>15819.386255381269</v>
+          </cell>
+          <cell r="AF91">
+            <v>15871.035385505404</v>
+          </cell>
+          <cell r="AG91">
+            <v>15922.684515629539</v>
+          </cell>
+          <cell r="AH91">
+            <v>15974.333645753673</v>
+          </cell>
+          <cell r="AI91">
+            <v>16025.982775877808</v>
+          </cell>
+          <cell r="AJ91">
+            <v>16077.631906001943</v>
           </cell>
         </row>
-        <row r="85">
-          <cell r="N85">
-            <v>2.3883468123093499E-2</v>
+        <row r="92">
+          <cell r="E92">
+            <v>28509.784963515838</v>
+          </cell>
+          <cell r="F92">
+            <v>29127.724124212171</v>
+          </cell>
+          <cell r="G92">
+            <v>29745.663284908504</v>
+          </cell>
+          <cell r="H92">
+            <v>30363.602445604836</v>
+          </cell>
+          <cell r="I92">
+            <v>30981.541606301169</v>
+          </cell>
+          <cell r="J92">
+            <v>31599.480766997502</v>
+          </cell>
+          <cell r="K92">
+            <v>32217.419927693834</v>
+          </cell>
+          <cell r="L92">
+            <v>32835.359088390163</v>
+          </cell>
+          <cell r="M92">
+            <v>33453.298249086496</v>
+          </cell>
+          <cell r="N92">
+            <v>34071.237409782829</v>
+          </cell>
+          <cell r="O92">
+            <v>34689.176570479161</v>
+          </cell>
+          <cell r="P92">
+            <v>35307.115731175494</v>
+          </cell>
+          <cell r="Q92">
+            <v>35925.054891871827</v>
+          </cell>
+          <cell r="R92">
+            <v>36542.99405256816</v>
+          </cell>
+          <cell r="S92">
+            <v>37160.933213264492</v>
+          </cell>
+          <cell r="T92">
+            <v>37778.872373960825</v>
+          </cell>
+          <cell r="U92">
+            <v>38396.811534657158</v>
+          </cell>
+          <cell r="V92">
+            <v>39014.75069535349</v>
+          </cell>
+          <cell r="W92">
+            <v>39632.689856049823</v>
+          </cell>
+          <cell r="X92">
+            <v>40250.629016746156</v>
+          </cell>
+          <cell r="Y92">
+            <v>40868.568177442488</v>
+          </cell>
+          <cell r="Z92">
+            <v>41486.507338138821</v>
+          </cell>
+          <cell r="AA92">
+            <v>42104.446498835154</v>
+          </cell>
+          <cell r="AB92">
+            <v>42722.385659531486</v>
+          </cell>
+          <cell r="AC92">
+            <v>43340.324820227819</v>
+          </cell>
+          <cell r="AD92">
+            <v>43958.263980924152</v>
+          </cell>
+          <cell r="AE92">
+            <v>44576.203141620485</v>
+          </cell>
+          <cell r="AF92">
+            <v>45194.142302316817</v>
+          </cell>
+          <cell r="AG92">
+            <v>45812.08146301315</v>
+          </cell>
+          <cell r="AH92">
+            <v>46430.020623709483</v>
+          </cell>
+          <cell r="AI92">
+            <v>47047.959784405815</v>
+          </cell>
+          <cell r="AJ92">
+            <v>47665.898945102148</v>
           </cell>
         </row>
       </sheetData>
@@ -2924,15 +3305,89 @@
       <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="10">
+        <row r="4">
+          <cell r="K4">
+            <v>3.8835168293443356E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>-3.3462559735330077E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="4">
+          <cell r="C4">
+            <v>0.63449793100934282</v>
+          </cell>
+          <cell r="D4">
+            <v>0.63972651023832128</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>0.95914986038640171</v>
+          </cell>
+          <cell r="D16">
+            <v>0.91453366351748455</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13" refreshError="1"/>
       <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="15">
+        <row r="56">
+          <cell r="I56">
+            <v>1.042</v>
+          </cell>
+          <cell r="J56">
+            <v>1.028</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16">
+        <row r="7">
+          <cell r="C7">
+            <v>0.39189939646309102</v>
+          </cell>
+          <cell r="D7">
+            <v>0.34910898091961506</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>0.80494672770980769</v>
+          </cell>
+          <cell r="D8">
+            <v>0.88189763966989509</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="66">
+          <cell r="C66">
+            <v>-1.1032875408231391E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="18">
+        <row r="43">
+          <cell r="C43">
+            <v>-8.4651570153405076E-2</v>
+          </cell>
+          <cell r="D43">
+            <v>4.6057662015736502E-2</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>6.0000000000000001E-3</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20" refreshError="1"/>
     </sheetDataSet>
@@ -3587,31 +4042,31 @@
       </c>
       <c r="B2" s="35">
         <f>'SYVbT-passenger'!B2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>4020355711.3318291</v>
+        <v>4087971726.0656734</v>
       </c>
       <c r="C2" s="35">
         <f>'SYVbT-passenger'!C2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>192588946.86420828</v>
+        <v>195827987.88538995</v>
       </c>
       <c r="D2" s="35">
         <f>'SYVbT-passenger'!D2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>92269768121.229858</v>
+        <v>93821599463.712402</v>
       </c>
       <c r="E2" s="35">
         <f>'SYVbT-passenger'!E2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>43021054904.607452</v>
+        <v>43744600901.817688</v>
       </c>
       <c r="F2" s="35">
         <f>'SYVbT-passenger'!F2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>15078221971.405336</v>
+        <v>15331813780.733315</v>
       </c>
       <c r="G2" s="35">
         <f>'SYVbT-passenger'!G2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>12153957896.826735</v>
+        <v>12358368216.518103</v>
       </c>
       <c r="H2" s="35">
         <f>'SYVbT-passenger'!H2*'AVLo-passengers'!$F2 * 'BAADTbVT-Passenger'!$C2</f>
-        <v>279722448.65724611</v>
+        <v>284426937.15722758</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3620,31 +4075,31 @@
       </c>
       <c r="B3" s="35">
         <f>'SYVbT-passenger'!B3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>22699072188.637726</v>
+        <v>22334262569.599674</v>
       </c>
       <c r="C3" s="35">
         <f>'SYVbT-passenger'!C3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>1082402549.4895105</v>
+        <v>1065006646.3246781</v>
       </c>
       <c r="D3" s="35">
         <f>'SYVbT-passenger'!D3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>518581330244.48285</v>
+        <v>510246916575.30066</v>
       </c>
       <c r="E3" s="35">
         <f>'SYVbT-passenger'!E3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>241790093713.46954</v>
+        <v>237904148453.60385</v>
       </c>
       <c r="F3" s="35">
         <f>'SYVbT-passenger'!F3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>84743730984.340378</v>
+        <v>83381766585.119904</v>
       </c>
       <c r="G3" s="35">
         <f>'SYVbT-passenger'!G3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>68308567174.362122</v>
+        <v>67210741582.16069</v>
       </c>
       <c r="H3" s="35">
         <f>'SYVbT-passenger'!H3*'AVLo-passengers'!$F3 * 'BAADTbVT-Passenger'!$C3</f>
-        <v>1572116658.3331099</v>
+        <v>1546850282.930464</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3727,11 +4182,11 @@
       </c>
       <c r="D6" s="35">
         <f>'SYVbT-passenger'!D6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>1754793.708498274</v>
+        <v>95.65437280919258</v>
       </c>
       <c r="E6" s="35">
         <f>'SYVbT-passenger'!E6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>1193329913.5271664</v>
+        <v>65048.799685163322</v>
       </c>
       <c r="F6" s="35">
         <f>'SYVbT-passenger'!F6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
@@ -3739,7 +4194,7 @@
       </c>
       <c r="G6" s="35">
         <f>'SYVbT-passenger'!G6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>701917.48339930957</v>
+        <v>38.261749123677035</v>
       </c>
       <c r="H6" s="35">
         <f>'SYVbT-passenger'!H6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
@@ -3811,19 +4266,19 @@
       </c>
       <c r="B10" s="35">
         <f>'SYVbT-freight'!B2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
-        <v>1215509745.1052349</v>
+        <v>1212303486.1632619</v>
       </c>
       <c r="C10" s="35">
         <f>'SYVbT-freight'!C2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
-        <v>13833360.912200373</v>
+        <v>13796871.416907646</v>
       </c>
       <c r="D10" s="35">
         <f>'SYVbT-freight'!D2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
-        <v>261176818.75096074</v>
+        <v>260487889.25950378</v>
       </c>
       <c r="E10" s="35">
         <f>'SYVbT-freight'!E2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
-        <v>27975724628.970745</v>
+        <v>27901930554.006714</v>
       </c>
       <c r="F10" s="35">
         <f>'SYVbT-freight'!F2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
@@ -3831,7 +4286,7 @@
       </c>
       <c r="G10" s="35">
         <f>'SYVbT-freight'!G2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
-        <v>1834094392.9569204</v>
+        <v>1829256437.8755062</v>
       </c>
       <c r="H10" s="35">
         <f>'SYVbT-freight'!H2*'AVLo-freight'!$E2*'BAADTbVT-Freight'!$B2</f>
@@ -3844,7 +4299,7 @@
       </c>
       <c r="B11" s="35">
         <f>'SYVbT-freight'!B3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
-        <v>19237388416.878094</v>
+        <v>18255781287.499283</v>
       </c>
       <c r="C11" s="35">
         <f>'SYVbT-freight'!C3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
@@ -3852,11 +4307,11 @@
       </c>
       <c r="D11" s="35">
         <f>'SYVbT-freight'!D3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
-        <v>4133541444.6733289</v>
+        <v>3922623327.1125145</v>
       </c>
       <c r="E11" s="35">
         <f>'SYVbT-freight'!E3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
-        <v>442760646797.2326</v>
+        <v>420168338627.00183</v>
       </c>
       <c r="F11" s="35">
         <f>'SYVbT-freight'!F3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
@@ -3864,7 +4319,7 @@
       </c>
       <c r="G11" s="35">
         <f>'SYVbT-freight'!G3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
-        <v>29027481163.860046</v>
+        <v>27546324686.645332</v>
       </c>
       <c r="H11" s="35">
         <f>'SYVbT-freight'!H3*'AVLo-freight'!$E3*'BAADTbVT-Freight'!$B3</f>
@@ -3951,11 +4406,11 @@
       </c>
       <c r="D14" s="35">
         <f>'SYVbT-freight'!D6*'AVLo-freight'!$E6*'BAADTbVT-Freight'!$B6</f>
-        <v>10981211880.359722</v>
+        <v>328628302.68698394</v>
       </c>
       <c r="E14" s="35">
         <f>'SYVbT-freight'!E6*'AVLo-freight'!$E6*'BAADTbVT-Freight'!$B6</f>
-        <v>3279007437414.4219</v>
+        <v>98128936987.617706</v>
       </c>
       <c r="F14" s="35">
         <f>'SYVbT-freight'!F6*'AVLo-freight'!$E6*'BAADTbVT-Freight'!$B6</f>
@@ -3963,7 +4418,7 @@
       </c>
       <c r="G14" s="35">
         <f>'SYVbT-freight'!G6*'AVLo-freight'!$E6*'BAADTbVT-Freight'!$B6</f>
-        <v>4392484752.1438894</v>
+        <v>131451321.07479358</v>
       </c>
       <c r="H14" s="35">
         <f>'SYVbT-freight'!H6*'AVLo-freight'!$E6*'BAADTbVT-Freight'!$B6</f>
@@ -4135,131 +4590,131 @@
       </c>
       <c r="B2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!B2</f>
-        <v>167015670000.92267</v>
+        <v>169824609013.88977</v>
       </c>
       <c r="C2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!C2</f>
-        <v>171317068972.07626</v>
+        <v>173926106112.3497</v>
       </c>
       <c r="D2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!D2</f>
-        <v>175729248165.88165</v>
+        <v>178027603210.80963</v>
       </c>
       <c r="E2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!E2</f>
-        <v>180255060667.5358</v>
+        <v>182129100309.26956</v>
       </c>
       <c r="F2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!F2</f>
-        <v>184897433041.91409</v>
+        <v>186230597407.72949</v>
       </c>
       <c r="G2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!G2</f>
-        <v>189659367226.00015</v>
+        <v>190332094506.18942</v>
       </c>
       <c r="H2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!H2</f>
-        <v>194543942470.05389</v>
+        <v>194433591604.64935</v>
       </c>
       <c r="I2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!I2</f>
-        <v>199554317328.77365</v>
+        <v>198535088703.10928</v>
       </c>
       <c r="J2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!J2</f>
-        <v>204693731703.7392</v>
+        <v>202636585801.56921</v>
       </c>
       <c r="K2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!K2</f>
-        <v>209965508938.45728</v>
+        <v>206738082900.02914</v>
       </c>
       <c r="L2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!L2</f>
-        <v>215373057967.36356</v>
+        <v>210839579998.48907</v>
       </c>
       <c r="M2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!M2</f>
-        <v>220919875520.17102</v>
+        <v>214941077096.94904</v>
       </c>
       <c r="N2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!N2</f>
-        <v>226609548382.99039</v>
+        <v>219042574195.40897</v>
       </c>
       <c r="O2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!O2</f>
-        <v>232445755717.68411</v>
+        <v>223144071293.8689</v>
       </c>
       <c r="P2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!P2</f>
-        <v>238432271440.95456</v>
+        <v>227245568392.32883</v>
       </c>
       <c r="Q2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!Q2</f>
-        <v>244572966664.70377</v>
+        <v>231347065490.78876</v>
       </c>
       <c r="R2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!R2</f>
-        <v>250871812199.2439</v>
+        <v>235448562589.24869</v>
       </c>
       <c r="S2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!S2</f>
-        <v>257332881120.97623</v>
+        <v>239550059687.70862</v>
       </c>
       <c r="T2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!T2</f>
-        <v>263960351406.1994</v>
+        <v>243651556786.16858</v>
       </c>
       <c r="U2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!U2</f>
-        <v>270758508632.75003</v>
+        <v>247753053884.62851</v>
       </c>
       <c r="V2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!V2</f>
-        <v>277731748751.22247</v>
+        <v>251854550983.08844</v>
       </c>
       <c r="W2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!W2</f>
-        <v>284884580927.56018</v>
+        <v>255956048081.54837</v>
       </c>
       <c r="X2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!X2</f>
-        <v>292221630458.85602</v>
+        <v>260057545180.00833</v>
       </c>
       <c r="Y2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!Y2</f>
-        <v>299747641764.24799</v>
+        <v>264159042278.46826</v>
       </c>
       <c r="Z2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!Z2</f>
-        <v>307467481452.84326</v>
+        <v>268260539376.92819</v>
       </c>
       <c r="AA2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AA2</f>
-        <v>315386141470.65558</v>
+        <v>272362036475.38812</v>
       </c>
       <c r="AB2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AB2</f>
-        <v>323508742328.58997</v>
+        <v>276463533573.84802</v>
       </c>
       <c r="AC2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AC2</f>
-        <v>331840536413.56238</v>
+        <v>280565030672.30798</v>
       </c>
       <c r="AD2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AD2</f>
-        <v>340386911384.89575</v>
+        <v>284666527770.76788</v>
       </c>
       <c r="AE2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AE2</f>
-        <v>349153393658.18811</v>
+        <v>288768024869.22784</v>
       </c>
       <c r="AF2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AF2</f>
-        <v>358145651978.90625</v>
+        <v>292869521967.68774</v>
       </c>
       <c r="AG2" s="69">
         <f>SUM(Total_CargoDistance!$B2:$H2)*BCDTRTSY_Passenger!AG2</f>
-        <v>367369501088.01489</v>
+        <v>296971019066.14771</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -4268,131 +4723,131 @@
       </c>
       <c r="B3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!B3</f>
-        <v>938777313513.11511</v>
+        <v>923689692695.03979</v>
       </c>
       <c r="C3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!C3</f>
-        <v>896349526296.48083</v>
+        <v>882666502058.35083</v>
       </c>
       <c r="D3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!D3</f>
-        <v>855839251467.70288</v>
+        <v>843465245977.52319</v>
       </c>
       <c r="E3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!E3</f>
-        <v>817159827572.13599</v>
+        <v>806005008134.87622</v>
       </c>
       <c r="F3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!F3</f>
-        <v>780228509796.17883</v>
+        <v>770208465893.10889</v>
       </c>
       <c r="G3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!G3</f>
-        <v>744966292955.74023</v>
+        <v>736001730691.66235</v>
       </c>
       <c r="H3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!H3</f>
-        <v>711297742484.69238</v>
+        <v>703314195531.44763</v>
       </c>
       <c r="I3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!I3</f>
-        <v>679150833061.75684</v>
+        <v>672078389233.12854</v>
       </c>
       <c r="J3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!J3</f>
-        <v>648456794530.60352</v>
+        <v>642229837168.13098</v>
       </c>
       <c r="K3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!K3</f>
-        <v>619149964783.54993</v>
+        <v>613706928174.90881</v>
       </c>
       <c r="L3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!L3</f>
-        <v>591167649294.14172</v>
+        <v>586450787385.76599</v>
       </c>
       <c r="M3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!M3</f>
-        <v>564449986998.12012</v>
+        <v>560405154701.73267</v>
       </c>
       <c r="N3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!N3</f>
-        <v>538939822235.8634</v>
+        <v>535516268664.65265</v>
       </c>
       <c r="O3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!O3</f>
-        <v>514582582482.35449</v>
+        <v>511732755486.77911</v>
       </c>
       <c r="P3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!P3</f>
-        <v>491326161603.10992</v>
+        <v>489005523008.82263</v>
       </c>
       <c r="Q3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!Q3</f>
-        <v>469120808386.32574</v>
+        <v>467287659367.56647</v>
       </c>
       <c r="R3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!R3</f>
-        <v>447919020112.78278</v>
+        <v>446534336163.8866</v>
       </c>
       <c r="S3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!S3</f>
-        <v>427675440935.83136</v>
+        <v>426702715931.30444</v>
       </c>
       <c r="T3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!T3</f>
-        <v>408346764854.06512</v>
+        <v>407751863714.07385</v>
       </c>
       <c r="U3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!U3</f>
-        <v>389891643069.11877</v>
+        <v>389642662572.28925</v>
       </c>
       <c r="V3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!V3</f>
-        <v>372270595530.40509</v>
+        <v>372337732839.60748</v>
       </c>
       <c r="W3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!W3</f>
-        <v>355445926477.5636</v>
+        <v>355801354966.91992</v>
       </c>
       <c r="X3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!X3</f>
-        <v>339381643799.94556</v>
+        <v>339999395792.71576</v>
       </c>
       <c r="Y3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!Y3</f>
-        <v>324043382040.62524</v>
+        <v>324899238087.94794</v>
       </c>
       <c r="Z3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!Z3</f>
-        <v>309398328880.22406</v>
+        <v>310469713229.97455</v>
       </c>
       <c r="AA3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AA3</f>
-        <v>295415154943.27844</v>
+        <v>296681036866.60583</v>
       </c>
       <c r="AB3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AB3</f>
-        <v>282063946776.99017</v>
+        <v>283504747437.45923</v>
       </c>
       <c r="AC3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AC3</f>
-        <v>269316142858.98355</v>
+        <v>270913647425.72284</v>
       </c>
       <c r="AD3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AD3</f>
-        <v>257144472497.17517</v>
+        <v>258881747219.06387</v>
       </c>
       <c r="AE3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AE3</f>
-        <v>245522897491.04739</v>
+        <v>247384211463.80341</v>
       </c>
       <c r="AF3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AF3</f>
-        <v>234426556429.52454</v>
+        <v>236397307801.62607</v>
       </c>
       <c r="AG3" s="69">
         <f>SUM(Total_CargoDistance!$B3:$H3)*BCDTRTSY_Passenger!AG3</f>
-        <v>223831711506.29214</v>
+        <v>225898357883.01099</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -4667,131 +5122,131 @@
       </c>
       <c r="B6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!B6</f>
-        <v>1195786624.719064</v>
+        <v>65182.715807096189</v>
       </c>
       <c r="C6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!C6</f>
-        <v>1182593659.873709</v>
+        <v>64463.563024826341</v>
       </c>
       <c r="D6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!D6</f>
-        <v>1169546251.3657579</v>
+        <v>63752.344565602762</v>
       </c>
       <c r="E6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!E6</f>
-        <v>1156642793.2902756</v>
+        <v>63048.972891027821</v>
       </c>
       <c r="F6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!F6</f>
-        <v>1143881697.4600751</v>
+        <v>62353.361428504155</v>
       </c>
       <c r="G6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!G6</f>
-        <v>1131261393.2102418</v>
+        <v>61665.424560579042</v>
       </c>
       <c r="H6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!H6</f>
-        <v>1118780327.2048109</v>
+        <v>60985.07761440648</v>
       </c>
       <c r="I6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!I6</f>
-        <v>1106436963.24558</v>
+        <v>60312.236851325411</v>
       </c>
       <c r="J6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!J6</f>
-        <v>1094229782.0830295</v>
+        <v>59646.819456552999</v>
       </c>
       <c r="K6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!K6</f>
-        <v>1082157281.2293313</v>
+        <v>58988.743528991574</v>
       </c>
       <c r="L6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!L6</f>
-        <v>1070217974.7734176</v>
+        <v>58337.928071148097</v>
       </c>
       <c r="M6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!M6</f>
-        <v>1058410393.1980928</v>
+        <v>57694.292979164755</v>
       </c>
       <c r="N6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!N6</f>
-        <v>1046733083.1991611</v>
+        <v>57057.759032959635</v>
       </c>
       <c r="O6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!O6</f>
-        <v>1035184607.5065508</v>
+        <v>56428.2478864761</v>
       </c>
       <c r="P6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!P6</f>
-        <v>1023763544.707412</v>
+        <v>55805.682058039805</v>
       </c>
       <c r="Q6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Q6</f>
-        <v>1012468489.0711658</v>
+        <v>55189.984920822084</v>
       </c>
       <c r="R6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!R6</f>
-        <v>1001298050.3764833</v>
+        <v>54581.080693408483</v>
       </c>
       <c r="S6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!S6</f>
-        <v>990250853.74017465</v>
+        <v>53978.894430471482</v>
       </c>
       <c r="T6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!T6</f>
-        <v>979325539.44796455</v>
+        <v>53383.35201354602</v>
       </c>
       <c r="U6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!U6</f>
-        <v>968520762.7871362</v>
+        <v>52794.380141906804</v>
       </c>
       <c r="V6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!V6</f>
-        <v>957835193.88102055</v>
+        <v>52211.906323546347</v>
       </c>
       <c r="W6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!W6</f>
-        <v>947267517.52531207</v>
+        <v>51635.858866252413</v>
       </c>
       <c r="X6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!X6</f>
-        <v>936816433.02619064</v>
+        <v>51066.166868784028</v>
       </c>
       <c r="Y6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Y6</f>
-        <v>926480654.04022896</v>
+        <v>50502.760212144778</v>
       </c>
       <c r="Z6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Z6</f>
-        <v>916258908.41606629</v>
+        <v>49945.569550952401</v>
       </c>
       <c r="AA6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AA6</f>
-        <v>906149938.03782976</v>
+        <v>49394.526304903586</v>
       </c>
       <c r="AB6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AB6</f>
-        <v>896152498.67028189</v>
+        <v>48849.562650332977</v>
       </c>
       <c r="AC6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AC6</f>
-        <v>886265359.80567741</v>
+        <v>48310.61151186526</v>
       </c>
       <c r="AD6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AD6</f>
-        <v>876487304.51230991</v>
+        <v>47777.606554159385</v>
       </c>
       <c r="AE6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AE6</f>
-        <v>866817129.28472912</v>
+        <v>47250.48217374384</v>
       </c>
       <c r="AF6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AF6</f>
-        <v>857253643.89560986</v>
+        <v>46729.17349094207</v>
       </c>
       <c r="AG6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AG6</f>
-        <v>847795671.24925733</v>
+        <v>46213.616341886875</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -5034,131 +5489,131 @@
       </c>
       <c r="B10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!B2</f>
-        <v>31300338946.69606</v>
+        <v>31217775238.721893</v>
       </c>
       <c r="C10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!C2</f>
-        <v>31433711964.996204</v>
+        <v>31329153676.004673</v>
       </c>
       <c r="D10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!D2</f>
-        <v>31567653295.417217</v>
+        <v>31440532113.287445</v>
       </c>
       <c r="E10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!E2</f>
-        <v>31702165359.578323</v>
+        <v>31551910550.570225</v>
       </c>
       <c r="F10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!F2</f>
-        <v>31837250589.417461</v>
+        <v>31663288987.853001</v>
       </c>
       <c r="G10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!G2</f>
-        <v>31972911427.235222</v>
+        <v>31774667425.13578</v>
       </c>
       <c r="H10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!H2</f>
-        <v>32109150325.739029</v>
+        <v>31886045862.418552</v>
       </c>
       <c r="I10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!I2</f>
-        <v>32245969748.087456</v>
+        <v>31997424299.701332</v>
       </c>
       <c r="J10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!J2</f>
-        <v>32383372167.934784</v>
+        <v>32108802736.984112</v>
       </c>
       <c r="K10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!K2</f>
-        <v>32521360069.475716</v>
+        <v>32220181174.266888</v>
       </c>
       <c r="L10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!L2</f>
-        <v>32659935947.49028</v>
+        <v>32331559611.54966</v>
       </c>
       <c r="M10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!M2</f>
-        <v>32799102307.38895</v>
+        <v>32442938048.832439</v>
       </c>
       <c r="N10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!N2</f>
-        <v>32938861665.257931</v>
+        <v>32554316486.115219</v>
       </c>
       <c r="O10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!O2</f>
-        <v>33079216547.904659</v>
+        <v>32665694923.397999</v>
       </c>
       <c r="P10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!P2</f>
-        <v>33220169492.903481</v>
+        <v>32777073360.680771</v>
       </c>
       <c r="Q10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!Q2</f>
-        <v>33361723048.641529</v>
+        <v>32888451797.963547</v>
       </c>
       <c r="R10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!R2</f>
-        <v>33503879774.364799</v>
+        <v>32999830235.246326</v>
       </c>
       <c r="S10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!S2</f>
-        <v>33646642240.224419</v>
+        <v>33111208672.529106</v>
       </c>
       <c r="T10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!T2</f>
-        <v>33790013027.323124</v>
+        <v>33222587109.811878</v>
       </c>
       <c r="U10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!U2</f>
-        <v>33933994727.761902</v>
+        <v>33333965547.094658</v>
       </c>
       <c r="V10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!V2</f>
-        <v>34078589944.686878</v>
+        <v>33445343984.377438</v>
       </c>
       <c r="W10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!W2</f>
-        <v>34223801292.33638</v>
+        <v>33556722421.660213</v>
       </c>
       <c r="X10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!X2</f>
-        <v>34369631396.088188</v>
+        <v>33668100858.942986</v>
       </c>
       <c r="Y10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!Y2</f>
-        <v>34516082892.507004</v>
+        <v>33779479296.225765</v>
       </c>
       <c r="Z10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!Z2</f>
-        <v>34663158429.392128</v>
+        <v>33890857733.508545</v>
       </c>
       <c r="AA10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AA2</f>
-        <v>34810860665.825325</v>
+        <v>34002236170.791325</v>
       </c>
       <c r="AB10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AB2</f>
-        <v>34959192272.218903</v>
+        <v>34113614608.074097</v>
       </c>
       <c r="AC10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AC2</f>
-        <v>35108155930.363991</v>
+        <v>34224993045.356873</v>
       </c>
       <c r="AD10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AD2</f>
-        <v>35257754333.479019</v>
+        <v>34336371482.639652</v>
       </c>
       <c r="AE10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AE2</f>
-        <v>35407990186.258415</v>
+        <v>34447749919.922432</v>
       </c>
       <c r="AF10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AF2</f>
-        <v>35558866204.921524</v>
+        <v>34559128357.2052</v>
       </c>
       <c r="AG10" s="69">
         <f>SUM(Total_CargoDistance!$B10:$H10)*BCDTRTSY_freight!AG2</f>
-        <v>35710385117.261673</v>
+        <v>34670506794.487984</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -5167,131 +5622,131 @@
       </c>
       <c r="B11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!B3</f>
-        <v>495159057822.6441</v>
+        <v>469893067928.25897</v>
       </c>
       <c r="C11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!C3</f>
-        <v>506985173396.01221</v>
+        <v>480077828296.82001</v>
       </c>
       <c r="D11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!D3</f>
-        <v>519093737623.69696</v>
+        <v>490262588665.38098</v>
       </c>
       <c r="E11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!E3</f>
-        <v>531491496359.13</v>
+        <v>500447349033.94208</v>
       </c>
       <c r="F11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!F3</f>
-        <v>544185356570.11853</v>
+        <v>510632109402.50311</v>
       </c>
       <c r="G11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!G3</f>
-        <v>557182390186.81519</v>
+        <v>520816869771.06409</v>
       </c>
       <c r="H11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!H3</f>
-        <v>570489838041.59106</v>
+        <v>531001630139.62512</v>
       </c>
       <c r="I11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!I3</f>
-        <v>584115113903.00623</v>
+        <v>541186390508.1861</v>
       </c>
       <c r="J11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!J3</f>
-        <v>598065808606.12573</v>
+        <v>551371150876.74707</v>
       </c>
       <c r="K11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!K3</f>
-        <v>612349694281.4823</v>
+        <v>561555911245.30811</v>
       </c>
       <c r="L11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!L3</f>
-        <v>626974728685.04016</v>
+        <v>571740671613.86926</v>
       </c>
       <c r="M11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!M3</f>
-        <v>641949059631.57446</v>
+        <v>581925431982.4303</v>
       </c>
       <c r="N11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!N3</f>
-        <v>657281029533.93506</v>
+        <v>592110192350.99121</v>
       </c>
       <c r="O11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!O3</f>
-        <v>672979180050.72278</v>
+        <v>602294952719.55225</v>
       </c>
       <c r="P11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!P3</f>
-        <v>689052256844.96985</v>
+        <v>612479713088.11328</v>
       </c>
       <c r="Q11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!Q3</f>
-        <v>705509214456.47241</v>
+        <v>622664473456.67432</v>
       </c>
       <c r="R11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!R3</f>
-        <v>722359221290.49231</v>
+        <v>632849233825.23535</v>
       </c>
       <c r="S11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!S3</f>
-        <v>739611664725.60632</v>
+        <v>643033994193.79639</v>
       </c>
       <c r="T11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!T3</f>
-        <v>757276156343.54846</v>
+        <v>653218754562.35742</v>
       </c>
       <c r="U11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!U3</f>
-        <v>775362537283.95837</v>
+        <v>663403514930.91833</v>
       </c>
       <c r="V11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!V3</f>
-        <v>793880883727.02063</v>
+        <v>673588275299.47949</v>
       </c>
       <c r="W11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!W3</f>
-        <v>812841512507.04834</v>
+        <v>683773035668.04053</v>
       </c>
       <c r="X11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!X3</f>
-        <v>832254986860.13745</v>
+        <v>693957796036.60156</v>
       </c>
       <c r="Y11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!Y3</f>
-        <v>852132122309.09717</v>
+        <v>704142556405.16248</v>
       </c>
       <c r="Z11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!Z3</f>
-        <v>872483992688.93066</v>
+        <v>714327316773.72351</v>
       </c>
       <c r="AA11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AA3</f>
-        <v>893321936316.22595</v>
+        <v>724512077142.28467</v>
       </c>
       <c r="AB11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AB3</f>
-        <v>914657562305.89465</v>
+        <v>734696837510.84558</v>
       </c>
       <c r="AC11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AC3</f>
-        <v>936502757038.77393</v>
+        <v>744881597879.40662</v>
       </c>
       <c r="AD11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AD3</f>
-        <v>958869690783.69873</v>
+        <v>755066358247.96765</v>
       </c>
       <c r="AE11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AE3</f>
-        <v>981770824477.73169</v>
+        <v>765251118616.52881</v>
       </c>
       <c r="AF11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AF3</f>
-        <v>1005218916668.3287</v>
+        <v>775435878985.08972</v>
       </c>
       <c r="AG11" s="69">
         <f>SUM(Total_CargoDistance!$B11:$H11)*BCDTRTSY_freight!AG3</f>
-        <v>1029227030621.3074</v>
+        <v>785620639353.65076</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -5566,131 +6021,131 @@
       </c>
       <c r="B14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!B6</f>
-        <v>3294381134046.9258</v>
+        <v>98589016611.379486</v>
       </c>
       <c r="C14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!C6</f>
-        <v>3015506598366.0981</v>
+        <v>90243301555.346085</v>
       </c>
       <c r="D14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!D6</f>
-        <v>3154393782079.8672</v>
+        <v>94399697037.566391</v>
       </c>
       <c r="E14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!E6</f>
-        <v>3299677784759.4424</v>
+        <v>98747526378.11055</v>
       </c>
       <c r="F14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!F6</f>
-        <v>3319475851467.999</v>
+        <v>99340011536.379211</v>
       </c>
       <c r="G14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!G6</f>
-        <v>3339392706576.8076</v>
+        <v>99936051605.597488</v>
       </c>
       <c r="H14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!H6</f>
-        <v>3359429062816.2686</v>
+        <v>100535667915.23108</v>
       </c>
       <c r="I14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!I6</f>
-        <v>3379585637193.166</v>
+        <v>101138881922.72247</v>
       </c>
       <c r="J14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!J6</f>
-        <v>3399863151016.3252</v>
+        <v>101745715214.2588</v>
       </c>
       <c r="K14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!K6</f>
-        <v>3420262329922.4229</v>
+        <v>102356189505.54436</v>
       </c>
       <c r="L14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!L6</f>
-        <v>3440783903901.9575</v>
+        <v>102970326642.57762</v>
       </c>
       <c r="M14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!M6</f>
-        <v>3461428607325.3687</v>
+        <v>103588148602.43307</v>
       </c>
       <c r="N14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!N6</f>
-        <v>3482197178969.3208</v>
+        <v>104209677494.04767</v>
       </c>
       <c r="O14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!O6</f>
-        <v>3503090362043.1367</v>
+        <v>104834935559.01195</v>
       </c>
       <c r="P14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!P6</f>
-        <v>3524108904215.3955</v>
+        <v>105463945172.36603</v>
       </c>
       <c r="Q14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!Q6</f>
-        <v>3545253557640.6875</v>
+        <v>106096728843.40021</v>
       </c>
       <c r="R14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!R6</f>
-        <v>3566525078986.5322</v>
+        <v>106733309216.46063</v>
       </c>
       <c r="S14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!S6</f>
-        <v>3587924229460.4512</v>
+        <v>107373709071.75938</v>
       </c>
       <c r="T14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!T6</f>
-        <v>3609451774837.2139</v>
+        <v>108017951326.18994</v>
       </c>
       <c r="U14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!U6</f>
-        <v>3631108485486.2373</v>
+        <v>108666059034.14709</v>
       </c>
       <c r="V14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!V6</f>
-        <v>3652895136399.1553</v>
+        <v>109318055388.35197</v>
       </c>
       <c r="W14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!W6</f>
-        <v>3674812507217.5503</v>
+        <v>109973963720.6821</v>
       </c>
       <c r="X14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!X6</f>
-        <v>3696861382260.8555</v>
+        <v>110633807503.00618</v>
       </c>
       <c r="Y14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!Y6</f>
-        <v>3719042550554.4204</v>
+        <v>111297610348.02423</v>
       </c>
       <c r="Z14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!Z6</f>
-        <v>3741356805857.7471</v>
+        <v>111965396010.11237</v>
       </c>
       <c r="AA14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AA6</f>
-        <v>3763804946692.8931</v>
+        <v>112637188386.17303</v>
       </c>
       <c r="AB14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AB6</f>
-        <v>3786387776373.0503</v>
+        <v>113313011516.49007</v>
       </c>
       <c r="AC14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AC6</f>
-        <v>3809106103031.2891</v>
+        <v>113992889585.58902</v>
       </c>
       <c r="AD14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AD6</f>
-        <v>3831960739649.4766</v>
+        <v>114676846923.10254</v>
       </c>
       <c r="AE14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AE6</f>
-        <v>3854952504087.3735</v>
+        <v>115364908004.64116</v>
       </c>
       <c r="AF14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AF6</f>
-        <v>3878082219111.8979</v>
+        <v>116057097452.66901</v>
       </c>
       <c r="AG14" s="69">
         <f>SUM(Total_CargoDistance!$B14:$H14)*BCDTRTSY_freight!AG6</f>
-        <v>3901350712426.5693</v>
+        <v>116753440037.38504</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -7352,31 +7807,31 @@
       </c>
       <c r="C42" s="35">
         <f>IFERROR(Total_CargoDistance!B2/Road!C36, 0)</f>
-        <v>1.1227287272596604E-3</v>
+        <v>1.1416112460254815E-3</v>
       </c>
       <c r="D42" s="35">
         <f>IFERROR(Total_CargoDistance!C2/Road!D36, 0)</f>
-        <v>2.3751513184579043E-4</v>
+        <v>2.4150976013430963E-4</v>
       </c>
       <c r="E42" s="35">
         <f>IFERROR(Total_CargoDistance!D2/Road!E36, 0)</f>
-        <v>2.6596146694757815E-4</v>
+        <v>2.7043451753289681E-4</v>
       </c>
       <c r="F42" s="35">
         <f>IFERROR(Total_CargoDistance!E2/Road!F36, 0)</f>
-        <v>2.470843755995841E-4</v>
+        <v>2.5123994341015219E-4</v>
       </c>
       <c r="G42" s="35">
         <f>IFERROR(Total_CargoDistance!F2/Road!G36, 0)</f>
-        <v>2.4809496442741762E-4</v>
+        <v>2.5226752874127518E-4</v>
       </c>
       <c r="H42" s="35">
         <f>IFERROR(Total_CargoDistance!G2/Road!H36, 0)</f>
-        <v>2.7366940335396973E-4</v>
+        <v>2.782720892201053E-4</v>
       </c>
       <c r="I42" s="35">
         <f>IFERROR(Total_CargoDistance!H2/Road!I36, 0)</f>
-        <v>4.8902506219341646E-4</v>
+        <v>4.9724968911319105E-4</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -7385,31 +7840,31 @@
       </c>
       <c r="C43" s="35">
         <f>IFERROR(Total_CargoDistance!B3/Road!C37, 0)</f>
-        <v>1.1508828199598288E-2</v>
+        <v>1.1323863316620761E-2</v>
       </c>
       <c r="D43" s="35">
         <f>IFERROR(Total_CargoDistance!C3/Road!D37, 0)</f>
-        <v>2.3902010608540082E-3</v>
+        <v>2.3517867886234905E-3</v>
       </c>
       <c r="E43" s="35">
         <f>IFERROR(Total_CargoDistance!D3/Road!E37, 0)</f>
-        <v>2.7138685864419639E-3</v>
+        <v>2.670252470465435E-3</v>
       </c>
       <c r="F43" s="35">
         <f>IFERROR(Total_CargoDistance!E3/Road!F37, 0)</f>
-        <v>2.7150595465125793E-3</v>
+        <v>2.6714242899436046E-3</v>
       </c>
       <c r="G43" s="35">
         <f>IFERROR(Total_CargoDistance!F3/Road!G37, 0)</f>
-        <v>2.5315589440131738E-3</v>
+        <v>2.4908728293445708E-3</v>
       </c>
       <c r="H43" s="35">
         <f>IFERROR(Total_CargoDistance!G3/Road!H37, 0)</f>
-        <v>2.7540346298636689E-3</v>
+        <v>2.7097729827007914E-3</v>
       </c>
       <c r="I43" s="35">
         <f>IFERROR(Total_CargoDistance!H3/Road!I37, 0)</f>
-        <v>4.9212368633330004E-3</v>
+        <v>4.8421448841371633E-3</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -7418,19 +7873,19 @@
       </c>
       <c r="C44" s="35">
         <f>IFERROR(Total_CargoDistance!B10/Road!C38, 0)</f>
-        <v>6.5798820574477688E-4</v>
+        <v>6.5625257131084701E-4</v>
       </c>
       <c r="D44" s="35">
         <f>IFERROR(Total_CargoDistance!C10/Road!D38, 0)</f>
-        <v>1.5847326557973324E-4</v>
+        <v>1.5805524645082474E-4</v>
       </c>
       <c r="E44" s="35">
         <f>IFERROR(Total_CargoDistance!D10/Road!E38, 0)</f>
-        <v>1.0509496345551802E-4</v>
+        <v>1.0481774505583632E-4</v>
       </c>
       <c r="F44" s="35">
         <f>IFERROR(Total_CargoDistance!E10/Road!F38, 0)</f>
-        <v>1.0380732234767244E-4</v>
+        <v>1.0353350047428987E-4</v>
       </c>
       <c r="G44" s="35">
         <f>IFERROR(Total_CargoDistance!F10/Road!G38, 0)</f>
@@ -7438,7 +7893,7 @@
       </c>
       <c r="H44" s="35">
         <f>IFERROR(Total_CargoDistance!G10/Road!H38, 0)</f>
-        <v>1.3340249848135008E-4</v>
+        <v>1.3305061076069645E-4</v>
       </c>
       <c r="I44" s="35">
         <f>IFERROR(Total_CargoDistance!H10/Road!I38, 0)</f>
@@ -7451,7 +7906,7 @@
       </c>
       <c r="C45" s="35">
         <f>IFERROR(Total_CargoDistance!B11/Road!C39, 0)</f>
-        <v>6.2149365057914963E-2</v>
+        <v>5.8978131078270858E-2</v>
       </c>
       <c r="D45" s="35">
         <f>IFERROR(Total_CargoDistance!C11/Road!D39, 0)</f>
@@ -7459,11 +7914,11 @@
       </c>
       <c r="E45" s="35">
         <f>IFERROR(Total_CargoDistance!D11/Road!E39, 0)</f>
-        <v>9.9265992802289229E-3</v>
+        <v>9.4200845489772374E-3</v>
       </c>
       <c r="F45" s="35">
         <f>IFERROR(Total_CargoDistance!E11/Road!F39, 0)</f>
-        <v>1.0558702581861411E-2</v>
+        <v>1.0019934142677002E-2</v>
       </c>
       <c r="G45" s="35">
         <f>IFERROR(Total_CargoDistance!F11/Road!G39, 0)</f>
@@ -7471,7 +7926,7 @@
       </c>
       <c r="H45" s="35">
         <f>IFERROR(Total_CargoDistance!G11/Road!H39, 0)</f>
-        <v>1.2426694100178716E-2</v>
+        <v>1.1792609511407667E-2</v>
       </c>
       <c r="I45" s="35">
         <f>IFERROR(Total_CargoDistance!H11/Road!I39, 0)</f>
@@ -13820,11 +14275,11 @@
       </c>
       <c r="D2" s="35">
         <f>Total_CargoDistance!D6</f>
-        <v>1754793.708498274</v>
+        <v>95.65437280919258</v>
       </c>
       <c r="E2" s="35">
         <f>Total_CargoDistance!E6</f>
-        <v>1193329913.5271664</v>
+        <v>65048.799685163322</v>
       </c>
       <c r="F2" s="35">
         <f>Total_CargoDistance!F6</f>
@@ -13832,7 +14287,7 @@
       </c>
       <c r="G2" s="35">
         <f>Total_CargoDistance!G6</f>
-        <v>701917.48339930957</v>
+        <v>38.261749123677035</v>
       </c>
       <c r="H2" s="35">
         <f>Total_CargoDistance!H6</f>
@@ -13853,11 +14308,11 @@
       </c>
       <c r="D3" s="35">
         <f>Total_CargoDistance!D14</f>
-        <v>10981211880.359722</v>
+        <v>328628302.68698394</v>
       </c>
       <c r="E3" s="35">
         <f>Total_CargoDistance!E14</f>
-        <v>3279007437414.4219</v>
+        <v>98128936987.617706</v>
       </c>
       <c r="F3" s="35">
         <f>Total_CargoDistance!F14</f>
@@ -13865,7 +14320,7 @@
       </c>
       <c r="G3" s="35">
         <f>Total_CargoDistance!G14</f>
-        <v>4392484752.1438894</v>
+        <v>131451321.07479358</v>
       </c>
       <c r="H3" s="35">
         <f>Total_CargoDistance!H14</f>
@@ -13912,11 +14367,11 @@
       </c>
       <c r="D6">
         <f>IFERROR(ships!D2/'SYFAFE-psgr'!D6, 0)</f>
-        <v>174616816121.8537</v>
+        <v>9518419.1436200682</v>
       </c>
       <c r="E6">
         <f>IFERROR(ships!E2/'SYFAFE-psgr'!E6, 0)</f>
-        <v>118746419635505.39</v>
+        <v>6472905754.4273901</v>
       </c>
       <c r="F6">
         <f>IFERROR(ships!F2/'SYFAFE-psgr'!F6, 0)</f>
@@ -13945,11 +14400,11 @@
       </c>
       <c r="D7">
         <f>IFERROR(ships!D3/'SYFAFE-frgt'!D6, 0)</f>
-        <v>2281400201389.1992</v>
+        <v>68274128948.663551</v>
       </c>
       <c r="E7">
         <f>IFERROR(ships!E3/'SYFAFE-frgt'!E6, 0)</f>
-        <v>681229750375137.13</v>
+        <v>20386764142677.254</v>
       </c>
       <c r="F7">
         <f>IFERROR(ships!F3/'SYFAFE-frgt'!F6, 0)</f>
@@ -20450,31 +20905,31 @@
       </c>
       <c r="B2" s="32">
         <f>Road!C42</f>
-        <v>1.1227287272596604E-3</v>
+        <v>1.1416112460254815E-3</v>
       </c>
       <c r="C2" s="32">
         <f>Road!D42</f>
-        <v>2.3751513184579043E-4</v>
+        <v>2.4150976013430963E-4</v>
       </c>
       <c r="D2" s="32">
         <f>Road!E42</f>
-        <v>2.6596146694757815E-4</v>
+        <v>2.7043451753289681E-4</v>
       </c>
       <c r="E2" s="32">
         <f>Road!F42</f>
-        <v>2.470843755995841E-4</v>
+        <v>2.5123994341015219E-4</v>
       </c>
       <c r="F2" s="32">
         <f>Road!G42</f>
-        <v>2.4809496442741762E-4</v>
+        <v>2.5226752874127518E-4</v>
       </c>
       <c r="G2" s="32">
         <f>Road!H42</f>
-        <v>2.7366940335396973E-4</v>
+        <v>2.782720892201053E-4</v>
       </c>
       <c r="H2" s="32">
         <f>Road!I42</f>
-        <v>4.8902506219341646E-4</v>
+        <v>4.9724968911319105E-4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -20483,31 +20938,31 @@
       </c>
       <c r="B3" s="32">
         <f>Road!C43</f>
-        <v>1.1508828199598288E-2</v>
+        <v>1.1323863316620761E-2</v>
       </c>
       <c r="C3" s="32">
         <f>Road!D43</f>
-        <v>2.3902010608540082E-3</v>
+        <v>2.3517867886234905E-3</v>
       </c>
       <c r="D3" s="32">
         <f>Road!E43</f>
-        <v>2.7138685864419639E-3</v>
+        <v>2.670252470465435E-3</v>
       </c>
       <c r="E3" s="32">
         <f>Road!F43</f>
-        <v>2.7150595465125793E-3</v>
+        <v>2.6714242899436046E-3</v>
       </c>
       <c r="F3" s="32">
         <f>Road!G43</f>
-        <v>2.5315589440131738E-3</v>
+        <v>2.4908728293445708E-3</v>
       </c>
       <c r="G3" s="32">
         <f>Road!H43</f>
-        <v>2.7540346298636689E-3</v>
+        <v>2.7097729827007914E-3</v>
       </c>
       <c r="H3" s="32">
         <f>Road!I43</f>
-        <v>4.9212368633330004E-3</v>
+        <v>4.8421448841371633E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -20723,19 +21178,19 @@
       </c>
       <c r="B2" s="32">
         <f>Road!C44</f>
-        <v>6.5798820574477688E-4</v>
+        <v>6.5625257131084701E-4</v>
       </c>
       <c r="C2" s="32">
         <f>Road!D44</f>
-        <v>1.5847326557973324E-4</v>
+        <v>1.5805524645082474E-4</v>
       </c>
       <c r="D2" s="32">
         <f>Road!E44</f>
-        <v>1.0509496345551802E-4</v>
+        <v>1.0481774505583632E-4</v>
       </c>
       <c r="E2" s="32">
         <f>Road!F44</f>
-        <v>1.0380732234767244E-4</v>
+        <v>1.0353350047428987E-4</v>
       </c>
       <c r="F2" s="32">
         <f>Road!G44</f>
@@ -20743,7 +21198,7 @@
       </c>
       <c r="G2" s="32">
         <f>Road!H44</f>
-        <v>1.3340249848135008E-4</v>
+        <v>1.3305061076069645E-4</v>
       </c>
       <c r="H2" s="32">
         <f>Road!I44</f>
@@ -20756,7 +21211,7 @@
       </c>
       <c r="B3" s="32">
         <f>Road!C45</f>
-        <v>6.2149365057914963E-2</v>
+        <v>5.8978131078270858E-2</v>
       </c>
       <c r="C3" s="32">
         <f>Road!D45</f>
@@ -20764,11 +21219,11 @@
       </c>
       <c r="D3" s="32">
         <f>Road!E45</f>
-        <v>9.9265992802289229E-3</v>
+        <v>9.4200845489772374E-3</v>
       </c>
       <c r="E3" s="32">
         <f>Road!F45</f>
-        <v>1.0558702581861411E-2</v>
+        <v>1.0019934142677002E-2</v>
       </c>
       <c r="F3" s="32">
         <f>Road!G45</f>
@@ -20776,7 +21231,7 @@
       </c>
       <c r="G3" s="32">
         <f>Road!H45</f>
-        <v>1.2426694100178716E-2</v>
+        <v>1.1792609511407667E-2</v>
       </c>
       <c r="H3" s="32">
         <f>Road!I45</f>
@@ -21639,111 +22094,147 @@
         <v>8</v>
       </c>
       <c r="B2" s="14">
+        <f>'[4]DV-psgr'!H41</f>
         <v>1.404094416519162</v>
       </c>
       <c r="C2" s="14">
+        <f>$B2</f>
         <v>1.404094416519162</v>
       </c>
       <c r="D2" s="14">
+        <f t="shared" ref="D2:AK7" si="0">$B2</f>
         <v>1.404094416519162</v>
       </c>
       <c r="E2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="F2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="G2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="H2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="I2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="J2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="K2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="L2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="M2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="N2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="O2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="P2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Q2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="R2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="S2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="T2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="U2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="V2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="W2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="X2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Y2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Z2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AA2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AB2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AC2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AD2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AE2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AF2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AG2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AH2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AI2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AJ2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AK2" s="14">
+        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
     </row>
@@ -21752,111 +22243,147 @@
         <v>9</v>
       </c>
       <c r="B3" s="15">
+        <f>'[4]DV-psgr'!H42</f>
         <v>14.731070293267342</v>
       </c>
       <c r="C3" s="14">
+        <f t="shared" ref="C3:R7" si="1">$B3</f>
         <v>14.731070293267342</v>
       </c>
       <c r="D3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="E3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="F3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="G3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="H3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="I3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="J3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="K3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="L3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="M3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="N3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="O3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="P3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Q3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="R3" s="14">
+        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="S3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="T3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="U3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="V3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="W3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="X3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Y3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Z3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AA3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AB3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AC3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AD3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AE3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AF3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AG3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AH3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AI3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AJ3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AK3" s="14">
+        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
     </row>
@@ -21865,111 +22392,147 @@
         <v>10</v>
       </c>
       <c r="B4" s="15">
+        <f>[4]BAADTbVT_air!K16</f>
         <v>155.72981935122084</v>
       </c>
       <c r="C4" s="14">
+        <f t="shared" si="1"/>
         <v>155.72981935122084</v>
       </c>
       <c r="D4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="E4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="F4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="G4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="H4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="I4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="J4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="K4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="L4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="M4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="N4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="O4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="P4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Q4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="R4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="S4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="T4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="U4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="V4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="W4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="X4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Y4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Z4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AA4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AB4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AC4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AD4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AE4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AF4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AG4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AH4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AI4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AJ4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AK4" s="14">
+        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
     </row>
@@ -21978,111 +22541,147 @@
         <v>11</v>
       </c>
       <c r="B5" s="15">
+        <f>[4]rail!D30</f>
         <v>382.85954795395736</v>
       </c>
       <c r="C5" s="14">
+        <f t="shared" si="1"/>
         <v>382.85954795395736</v>
       </c>
       <c r="D5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="E5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="F5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="G5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="H5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="I5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="J5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="K5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="L5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="M5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="N5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="O5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="P5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Q5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="R5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="S5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="T5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="U5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="V5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="W5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="X5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Y5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Z5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AA5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AB5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AC5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AD5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AE5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AF5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AG5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AH5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AI5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AJ5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AK5" s="14">
+        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
     </row>
@@ -22091,112 +22690,112 @@
         <v>12</v>
       </c>
       <c r="B6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="C6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="D6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="E6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="F6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="G6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="H6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="I6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="J6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="K6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="L6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="M6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="N6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="O6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="P6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="R6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="S6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="T6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="U6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="V6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="W6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="X6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AD6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AF6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AH6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AI6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
       <c r="AK6" s="14">
-        <v>337.61417769892506</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -22207,108 +22806,143 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="14">
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="E7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="F7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="G7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="H7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="J7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="K7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="L7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="M7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="N7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="O7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="P7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Q7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="R7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="S7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="T7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="U7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="V7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="W7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="X7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Y7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Z7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AA7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AB7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AC7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AD7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AE7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AF7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AG7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AH7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AI7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AJ7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AK7" s="14">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -22442,108 +23076,143 @@
         <v>8</v>
       </c>
       <c r="B2" s="17">
+        <f>'[4]DV-freight'!O10</f>
         <v>1.2304866591260886</v>
       </c>
       <c r="C2" s="17">
+        <f>$B$2</f>
         <v>1.2304866591260886</v>
       </c>
       <c r="D2" s="17">
+        <f t="shared" ref="D2:AJ2" si="0">$B$2</f>
         <v>1.2304866591260886</v>
       </c>
       <c r="E2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="F2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="G2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="H2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="I2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="J2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="K2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="L2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="M2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="N2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="O2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="P2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="Q2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="R2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="S2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="T2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="U2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="V2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="W2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="X2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="Y2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="Z2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AA2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AB2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AC2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AD2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AE2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AF2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AG2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AH2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AI2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
       <c r="AJ2" s="17">
+        <f t="shared" si="0"/>
         <v>1.2304866591260886</v>
       </c>
     </row>
@@ -22552,108 +23221,143 @@
         <v>9</v>
       </c>
       <c r="B3" s="18">
+        <f>'[4]DV-freight'!K10</f>
         <v>27.6</v>
       </c>
       <c r="C3" s="2">
+        <f t="shared" ref="C3:R7" si="1">$B3</f>
         <v>27.6</v>
       </c>
       <c r="D3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="E3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="F3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="G3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="H3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="I3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="J3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="K3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="L3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="M3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="N3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="O3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="P3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="Q3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="R3" s="2">
+        <f t="shared" si="1"/>
         <v>27.6</v>
       </c>
       <c r="S3" s="2">
+        <f t="shared" ref="S3:AJ7" si="2">$B3</f>
         <v>27.6</v>
       </c>
       <c r="T3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="U3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="V3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="W3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="X3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="Y3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="Z3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AA3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AB3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AC3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AD3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AE3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AF3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AG3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AH3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AI3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
       <c r="AJ3" s="2">
+        <f t="shared" si="2"/>
         <v>27.6</v>
       </c>
     </row>
@@ -22662,108 +23366,143 @@
         <v>10</v>
       </c>
       <c r="B4" s="18">
+        <f>[4]BAADTbVT_air!L7</f>
         <v>63.556825639903742</v>
       </c>
       <c r="C4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="D4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="E4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="F4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="G4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="H4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="I4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="J4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="K4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="L4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="M4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="N4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="O4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="P4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="Q4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="R4" s="10">
+        <f t="shared" si="1"/>
         <v>63.556825639903742</v>
       </c>
       <c r="S4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="T4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="U4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="V4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="W4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="X4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="Y4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="Z4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AA4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AB4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AC4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AD4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AE4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AF4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AG4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AH4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AI4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
       <c r="AJ4" s="10">
+        <f t="shared" si="2"/>
         <v>63.556825639903742</v>
       </c>
     </row>
@@ -22772,108 +23511,143 @@
         <v>11</v>
       </c>
       <c r="B5" s="18">
+        <f>[4]rail!C15</f>
         <v>1514.4</v>
       </c>
       <c r="C5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="D5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="E5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="F5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="G5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="H5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="I5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="J5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="K5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="L5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="M5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="N5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="O5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="P5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="Q5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="R5" s="10">
+        <f t="shared" si="1"/>
         <v>1514.4</v>
       </c>
       <c r="S5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="T5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="U5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="V5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="W5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="X5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="Y5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="Z5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AA5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AB5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AC5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AD5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AE5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AF5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AG5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AH5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AI5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
       <c r="AJ5" s="10">
+        <f t="shared" si="2"/>
         <v>1514.4</v>
       </c>
     </row>
@@ -22881,110 +23655,145 @@
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="18">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="C6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="D6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="E6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="F6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="G6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="H6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="I6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="J6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="K6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="L6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="M6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="N6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="O6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="P6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="R6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="S6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="T6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="U6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="V6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="W6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="X6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AG6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AH6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AI6" s="10">
-        <v>65977.620430441006</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>65977.620430441006</v>
+      <c r="B6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="C6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="D6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="E6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="F6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="G6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="H6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="I6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="J6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="K6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="L6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="M6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="N6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="O6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="P6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Q6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="R6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="S6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="T6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="U6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="V6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="W6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="X6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Y6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Z6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AA6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AB6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AC6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AD6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AE6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AF6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AG6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AH6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AI6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AJ6" s="105">
+        <f>'[4]US AVLo'!$B$14</f>
+        <v>1974.4736422180429</v>
       </c>
     </row>
     <row r="7" spans="1:36">
@@ -22995,105 +23804,139 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="C7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="F7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="H7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="I7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="K7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="L7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="M7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="N7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="O7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="P7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="R7" s="2">
+        <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="S7" s="2">
+        <f t="shared" ref="S7:AJ7" si="3">$B7</f>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="T7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="U7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="V7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="W7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="X7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="Y7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="Z7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AA7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AB7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AC7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AD7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AE7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AF7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AG7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AH7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AI7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="AJ7" s="2">
+        <f t="shared" si="3"/>
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
@@ -23113,94 +23956,94 @@
         <v>239</v>
       </c>
       <c r="B1" s="8">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="8">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="8">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="8">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="8">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="8">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="8">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="8">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="8">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="8">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="8">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="8">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="8">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="8">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="P1" s="8">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="Q1" s="8">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="R1" s="8">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="S1" s="8">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="T1" s="8">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="U1" s="8">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="V1" s="8">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="W1" s="8">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="X1" s="8">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="Y1" s="8">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="Z1" s="8">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="AA1" s="8">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="AB1" s="8">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="AC1" s="8">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="AD1" s="8">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="AE1" s="8">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="AF1" s="8">
         <v>2048</v>
@@ -23218,135 +24061,135 @@
       </c>
       <c r="B2" s="10">
         <f t="shared" ref="B2:B7" si="0">C2</f>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="C2" s="10">
-        <f>'[4]DV-Cal'!S4</f>
-        <v>7645.3386159425945</v>
+        <f>'[5]DV-Cal'!S4</f>
+        <v>7773.9211010803465</v>
       </c>
       <c r="D2" s="10">
         <f>$C$2</f>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="E2" s="10">
-        <f t="shared" ref="E2:AH2" si="1">$C$2</f>
-        <v>7645.3386159425945</v>
+        <f t="shared" ref="E2:AE2" si="1">$C$2</f>
+        <v>7773.9211010803465</v>
       </c>
       <c r="F2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="G2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="H2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="I2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="K2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="L2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="M2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="N2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="O2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="P2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="W2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AB2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AC2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AD2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AE2" s="10">
         <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AF2" s="10">
-        <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <f t="shared" ref="E2:AH2" si="2">$C$2</f>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AG2" s="10">
-        <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <f t="shared" si="2"/>
+        <v>7773.9211010803465</v>
       </c>
       <c r="AH2" s="10">
-        <f t="shared" si="1"/>
-        <v>7645.3386159425945</v>
+        <f t="shared" si="2"/>
+        <v>7773.9211010803465</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -23355,135 +24198,135 @@
       </c>
       <c r="B3" s="10">
         <f t="shared" si="0"/>
-        <v>9323.117790227654</v>
+        <v>9173.2806946391247</v>
       </c>
       <c r="C3" s="10">
-        <f>'[4]DV-Cal'!S7</f>
-        <v>9323.117790227654</v>
+        <f>'[5]DV-Cal'!S7</f>
+        <v>9173.2806946391247</v>
       </c>
       <c r="D3" s="10">
         <f>$C$3</f>
-        <v>9323.117790227654</v>
+        <v>9173.2806946391247</v>
       </c>
       <c r="E3" s="10">
-        <f t="shared" ref="E3:AH3" si="2">$C$3</f>
-        <v>9323.117790227654</v>
+        <f t="shared" ref="E3:AE3" si="3">$C$3</f>
+        <v>9173.2806946391247</v>
       </c>
       <c r="F3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="G3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="H3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="I3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="J3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="K3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="L3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="M3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="N3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="O3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="P3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="Q3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="R3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="S3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="T3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="U3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="V3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="W3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="X3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="Y3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="Z3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AA3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AB3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AC3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AD3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AE3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="3"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AF3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" ref="E3:AH3" si="4">$C$3</f>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AG3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="4"/>
+        <v>9173.2806946391247</v>
       </c>
       <c r="AH3" s="10">
-        <f t="shared" si="2"/>
-        <v>9323.117790227654</v>
+        <f t="shared" si="4"/>
+        <v>9173.2806946391247</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -23495,7 +24338,7 @@
         <v>1037079.5912426789</v>
       </c>
       <c r="C4" s="10">
-        <f>'[4]Air-Cal'!O4</f>
+        <f>'[5]Air-Cal'!O4</f>
         <v>1037079.5912426789</v>
       </c>
       <c r="D4" s="10">
@@ -23503,123 +24346,123 @@
         <v>1037079.5912426789</v>
       </c>
       <c r="E4" s="10">
-        <f t="shared" ref="E4:AH4" si="3">$C$4</f>
+        <f t="shared" ref="E4:AE4" si="5">$C$4</f>
         <v>1037079.5912426789</v>
       </c>
       <c r="F4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="G4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="H4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="I4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="J4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="K4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="L4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="M4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="N4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="O4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="P4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="Q4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="R4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="S4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="T4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="U4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="V4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="W4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="X4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="Y4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="Z4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AA4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AB4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AC4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AD4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AE4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AF4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E4:AH4" si="6">$C$4</f>
         <v>1037079.5912426789</v>
       </c>
       <c r="AG4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1037079.5912426789</v>
       </c>
       <c r="AH4" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1037079.5912426789</v>
       </c>
     </row>
@@ -23632,7 +24475,7 @@
         <v>87159.138758496847</v>
       </c>
       <c r="C5" s="10">
-        <f>'[4]Rail-Cal'!$G$14</f>
+        <f>'[5]Rail-Cal'!$G$14</f>
         <v>87159.138758496847</v>
       </c>
       <c r="D5" s="10">
@@ -23640,123 +24483,123 @@
         <v>87159.138758496847</v>
       </c>
       <c r="E5" s="10">
-        <f t="shared" ref="E5:AH5" si="4">$C$5</f>
+        <f t="shared" ref="E5:AE5" si="7">$C$5</f>
         <v>87159.138758496847</v>
       </c>
       <c r="F5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="G5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="H5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="I5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="J5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="K5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="L5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="M5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="N5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="O5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="P5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="Q5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="R5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="S5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="T5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="U5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="V5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="W5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="X5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="Y5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="Z5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AA5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AB5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AC5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AD5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AE5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AF5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E5:AH5" si="8">$C$5</f>
         <v>87159.138758496847</v>
       </c>
       <c r="AG5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>87159.138758496847</v>
       </c>
       <c r="AH5" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>87159.138758496847</v>
       </c>
     </row>
@@ -23765,136 +24608,106 @@
         <v>12</v>
       </c>
       <c r="B6" s="10">
-        <f t="shared" si="0"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="C6" s="10">
-        <f>'[4]Ships-Cal'!H69</f>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="D6" s="10">
-        <f>$C$6</f>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="E6" s="10">
-        <f t="shared" ref="E6:AH6" si="5">$C$6</f>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="F6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="G6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="H6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="K6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="L6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="M6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="N6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="O6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="P6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="Q6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="R6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="S6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="T6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="U6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="V6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="W6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="X6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="Y6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="Z6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AA6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AB6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AC6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AD6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AE6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <v>194.17552144824873</v>
       </c>
       <c r="AF6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <f t="shared" ref="E6:AH6" si="9">$C$6</f>
+        <v>194.17552144824873</v>
       </c>
       <c r="AG6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <f t="shared" si="9"/>
+        <v>194.17552144824873</v>
       </c>
       <c r="AH6" s="10">
-        <f t="shared" si="5"/>
-        <v>10551.03452890655</v>
+        <f t="shared" si="9"/>
+        <v>194.17552144824873</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -23906,131 +24719,131 @@
         <v>4543.5229764190408</v>
       </c>
       <c r="C7" s="10">
-        <f>[4]Motorbikes!$E$7*[4]About!$B$64*365</f>
+        <f>[5]Motorbikes!$E$7*[5]About!$B$64*365</f>
         <v>4543.5229764190408</v>
       </c>
       <c r="D7" s="10">
-        <f t="shared" ref="D7:AH7" si="6">$B$7</f>
+        <f t="shared" ref="D7:AE7" si="10">$B$7</f>
         <v>4543.5229764190408</v>
       </c>
       <c r="E7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="F7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="G7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="H7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="I7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="K7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="L7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="M7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="N7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="O7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="P7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="Q7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="R7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="S7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="T7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="U7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="V7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="W7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="X7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="Y7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="Z7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AA7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AB7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AC7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AD7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AE7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AF7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D7:AH7" si="11">$B$7</f>
         <v>4543.5229764190408</v>
       </c>
       <c r="AG7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4543.5229764190408</v>
       </c>
       <c r="AH7" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4543.5229764190408</v>
       </c>
     </row>
@@ -24050,94 +24863,94 @@
         <v>239</v>
       </c>
       <c r="B1" s="9">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="9">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="9">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="9">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="9">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="9">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="9">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="9">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="9">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="9">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="9">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="9">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="9">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="9">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="P1" s="9">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="Q1" s="9">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="R1" s="9">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="S1" s="9">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="T1" s="9">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="U1" s="9">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="V1" s="9">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="W1" s="9">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="X1" s="9">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="Y1" s="9">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="Z1" s="9">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="AA1" s="9">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="AB1" s="9">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="AC1" s="9">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="AD1" s="9">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="AE1" s="9">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="AF1" s="9">
         <v>2049</v>
@@ -24152,131 +24965,131 @@
       </c>
       <c r="B2" s="10">
         <f>C2</f>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="C2" s="10">
-        <f>'[4]DV-Cal'!S10</f>
-        <v>9169.809811392035</v>
+        <f>'[5]DV-Cal'!S10</f>
+        <v>9145.6217826062839</v>
       </c>
       <c r="D2" s="10">
         <f>$C$2</f>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="E2" s="10">
-        <f t="shared" ref="E2:AG2" si="0">$C$2</f>
-        <v>9169.809811392035</v>
+        <f t="shared" ref="E2:AE2" si="0">$C$2</f>
+        <v>9145.6217826062839</v>
       </c>
       <c r="F2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="G2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="H2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="I2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="K2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="L2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="M2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="N2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="O2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="P2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="W2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AB2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AC2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AD2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AE2" s="10">
         <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AF2" s="10">
-        <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <f t="shared" ref="E2:AG2" si="1">$C$2</f>
+        <v>9145.6217826062839</v>
       </c>
       <c r="AG2" s="10">
-        <f t="shared" si="0"/>
-        <v>9169.809811392035</v>
+        <f t="shared" si="1"/>
+        <v>9145.6217826062839</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -24285,131 +25098,131 @@
       </c>
       <c r="B3" s="10">
         <f>C3</f>
-        <v>18979.686196888564</v>
+        <v>18011.228582969787</v>
       </c>
       <c r="C3" s="10">
-        <f>'[4]DV-Cal'!S13</f>
-        <v>18979.686196888564</v>
+        <f>'[5]DV-Cal'!S13</f>
+        <v>18011.228582969787</v>
       </c>
       <c r="D3" s="10">
         <f>$C$3</f>
-        <v>18979.686196888564</v>
+        <v>18011.228582969787</v>
       </c>
       <c r="E3" s="10">
-        <f t="shared" ref="E3:AG3" si="1">$C$3</f>
-        <v>18979.686196888564</v>
+        <f t="shared" ref="E3:AE3" si="2">$C$3</f>
+        <v>18011.228582969787</v>
       </c>
       <c r="F3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="G3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="H3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="I3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="J3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="K3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="L3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="M3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="N3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="O3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="P3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="Q3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="R3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="S3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="T3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="U3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="V3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="W3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="X3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="Y3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="Z3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AA3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AB3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AC3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AD3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AE3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="2"/>
+        <v>18011.228582969787</v>
       </c>
       <c r="AF3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" ref="E3:AG3" si="3">$C$3</f>
+        <v>18011.228582969787</v>
       </c>
       <c r="AG3" s="10">
-        <f t="shared" si="1"/>
-        <v>18979.686196888564</v>
+        <f t="shared" si="3"/>
+        <v>18011.228582969787</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -24417,7 +25230,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="10">
-        <f>'[4]Air-Cal'!O7</f>
+        <f>'[5]Air-Cal'!O7</f>
         <v>3355599.9662397844</v>
       </c>
       <c r="C4" s="10">
@@ -24425,123 +25238,123 @@
         <v>3355599.9662397844</v>
       </c>
       <c r="D4" s="10">
-        <f t="shared" ref="D4:AG4" si="2">$B$4</f>
+        <f t="shared" ref="D4:AE4" si="4">$B$4</f>
         <v>3355599.9662397844</v>
       </c>
       <c r="E4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="F4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="G4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="H4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="I4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="J4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="K4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="L4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="M4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="N4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="O4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="P4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="Q4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="R4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="S4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="T4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="U4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="V4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="W4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="X4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="Y4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="Z4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AA4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AB4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AC4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AD4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AE4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3355599.9662397844</v>
       </c>
       <c r="AF4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D4:AG4" si="5">$B$4</f>
         <v>3355599.9662397844</v>
       </c>
       <c r="AG4" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3355599.9662397844</v>
       </c>
     </row>
@@ -24550,7 +25363,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="10">
-        <f>'[4]Rail-Cal'!G6</f>
+        <f>'[5]Rail-Cal'!G6</f>
         <v>15068.57360345372</v>
       </c>
       <c r="C5" s="10">
@@ -24558,123 +25371,123 @@
         <v>15068.57360345372</v>
       </c>
       <c r="D5" s="10">
-        <f t="shared" ref="D5:AG5" si="3">$B$5</f>
+        <f t="shared" ref="D5:AE5" si="6">$B$5</f>
         <v>15068.57360345372</v>
       </c>
       <c r="E5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="F5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="G5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="H5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="I5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="J5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="K5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="L5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="M5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="N5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="O5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="P5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="Q5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="R5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="S5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="T5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="U5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="V5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="W5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="X5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="Y5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="Z5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AA5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AB5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AC5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AD5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AE5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15068.57360345372</v>
       </c>
       <c r="AF5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D5:AG5" si="7">$B$5</f>
         <v>15068.57360345372</v>
       </c>
       <c r="AG5" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>15068.57360345372</v>
       </c>
     </row>
@@ -24683,131 +25496,131 @@
         <v>12</v>
       </c>
       <c r="B6" s="10">
-        <f>'[4]Ships-Cal'!H72</f>
+        <f>'[5]Ships-Cal'!H72</f>
         <v>81662.909988119718</v>
       </c>
       <c r="C6" s="10">
-        <f>$B$6</f>
+        <f>B6</f>
         <v>81662.909988119718</v>
       </c>
       <c r="D6" s="10">
-        <f t="shared" ref="D6:AG6" si="4">$B$6</f>
+        <f t="shared" ref="D6:AE7" si="8">C6</f>
         <v>81662.909988119718</v>
       </c>
       <c r="E6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="F6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="G6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="H6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="K6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="L6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="M6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="N6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="O6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="P6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="Q6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="R6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="S6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="T6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="U6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="V6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="W6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="X6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="Y6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="Z6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AA6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AB6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AC6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AD6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AE6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81662.909988119718</v>
       </c>
       <c r="AF6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D6:AG6" si="9">$B$6</f>
         <v>81662.909988119718</v>
       </c>
       <c r="AG6" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>81662.909988119718</v>
       </c>
     </row>
@@ -24816,131 +25629,131 @@
         <v>13</v>
       </c>
       <c r="B7" s="10">
-        <f>[4]Motorbikes!$E$2*[4]About!$B$64*365</f>
+        <f>[5]Motorbikes!$E$2*[5]About!$B$64*365</f>
         <v>10573.883538920783</v>
       </c>
       <c r="C7" s="10">
-        <f t="shared" ref="C7:AG7" si="5">B7</f>
+        <f t="shared" ref="C7" si="10">B7</f>
         <v>10573.883538920783</v>
       </c>
       <c r="D7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="E7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="F7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="G7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="H7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="I7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="K7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="L7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="M7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="N7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="O7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="P7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="Q7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="R7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="S7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="T7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="U7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="V7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="W7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="X7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="Y7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="Z7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AA7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AB7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AC7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AD7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AE7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10573.883538920783</v>
       </c>
       <c r="AF7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C7:AG7" si="11">AE7</f>
         <v>10573.883538920783</v>
       </c>
       <c r="AG7" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>10573.883538920783</v>
       </c>
     </row>
@@ -25064,128 +25877,128 @@
         <v>1</v>
       </c>
       <c r="C2" s="66">
-        <f>B2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.0257544634651936</v>
+        <f>$B$2*'[6]DV-CAGR'!F89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.0241513707717382</v>
       </c>
       <c r="D2" s="66">
-        <f>C2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.0521722193187673</v>
+        <f>$B$2*'[6]DV-CAGR'!G89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.0483027415434765</v>
       </c>
       <c r="E2" s="66">
-        <f>D2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.079270350300304</v>
+        <f>$B$2*'[6]DV-CAGR'!H89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.0724541123152147</v>
       </c>
       <c r="F2" s="66">
-        <f>E2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.1070663791061799</v>
+        <f>$B$2*'[6]DV-CAGR'!I89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.0966054830869529</v>
       </c>
       <c r="G2" s="66">
-        <f>F2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.1355782797204141</v>
+        <f>$B$2*'[6]DV-CAGR'!J89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.1207568538586912</v>
       </c>
       <c r="H2" s="66">
-        <f>G2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.1648244890373409</v>
+        <f>$B$2*'[6]DV-CAGR'!K89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.1449082246304294</v>
       </c>
       <c r="I2" s="66">
-        <f>H2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.194823918783616</v>
+        <f>$B$2*'[6]DV-CAGR'!L89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.1690595954021676</v>
       </c>
       <c r="J2" s="66">
-        <f>I2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.2255959677472681</v>
+        <f>$B$2*'[6]DV-CAGR'!M89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.1932109661739059</v>
       </c>
       <c r="K2" s="66">
-        <f>J2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.2571605343217036</v>
+        <f>$B$2*'[6]DV-CAGR'!N89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.2173623369456441</v>
       </c>
       <c r="L2" s="66">
-        <f>K2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.2895380293727752</v>
+        <f>$B$2*'[6]DV-CAGR'!O89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.2415137077173823</v>
       </c>
       <c r="M2" s="66">
-        <f>L2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.322749389437234</v>
+        <f>$B$2*'[6]DV-CAGR'!P89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.2656650784891208</v>
       </c>
       <c r="N2" s="66">
-        <f>M2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.3568160902611024</v>
+        <f>$B$2*'[6]DV-CAGR'!Q89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.289816449260859</v>
       </c>
       <c r="O2" s="66">
-        <f>N2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.3917601606867187</v>
+        <f>$B$2*'[6]DV-CAGR'!R89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.3139678200325973</v>
       </c>
       <c r="P2" s="66">
-        <f>O2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.4276041968974369</v>
+        <f>$B$2*'[6]DV-CAGR'!S89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.3381191908043355</v>
       </c>
       <c r="Q2" s="66">
-        <f>P2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.4643713770291891</v>
+        <f>$B$2*'[6]DV-CAGR'!T89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.3622705615760737</v>
       </c>
       <c r="R2" s="66">
-        <f>Q2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.5020854761583626</v>
+        <f>$B$2*'[6]DV-CAGR'!U89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.386421932347812</v>
       </c>
       <c r="S2" s="66">
-        <f>R2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.5407708816756811</v>
+        <f>$B$2*'[6]DV-CAGR'!V89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.4105733031195502</v>
       </c>
       <c r="T2" s="66">
-        <f>S2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.5804526090560316</v>
+        <f>$B$2*'[6]DV-CAGR'!W89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.4347246738912884</v>
       </c>
       <c r="U2" s="66">
-        <f>T2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.6211563180344351</v>
+        <f>$B$2*'[6]DV-CAGR'!X89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.4588760446630267</v>
       </c>
       <c r="V2" s="66">
-        <f>U2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.6629083291986206</v>
+        <f>$B$2*'[6]DV-CAGR'!Y89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.4830274154347649</v>
       </c>
       <c r="W2" s="66">
-        <f>V2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.7057356410089326</v>
+        <f>$B$2*'[6]DV-CAGR'!Z89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.5071787862065031</v>
       </c>
       <c r="X2" s="66">
-        <f>W2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.7496659472565759</v>
+        <f>$B$2*'[6]DV-CAGR'!AA89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.5313301569782416</v>
       </c>
       <c r="Y2" s="66">
-        <f>X2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.7947276549714888</v>
+        <f>$B$2*'[6]DV-CAGR'!AB89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.5554815277499798</v>
       </c>
       <c r="Z2" s="66">
-        <f>Y2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.8409499027914247</v>
+        <f>$B$2*'[6]DV-CAGR'!AC89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.5796328985217181</v>
       </c>
       <c r="AA2" s="66">
-        <f>Z2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.8883625798041181</v>
+        <f>$B$2*'[6]DV-CAGR'!AD89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.6037842692934563</v>
       </c>
       <c r="AB2" s="66">
-        <f>AA2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.9369963448747221</v>
+        <f>$B$2*'[6]DV-CAGR'!AE89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.6279356400651945</v>
       </c>
       <c r="AC2" s="66">
-        <f>AB2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>1.9868826464710116</v>
+        <f>$B$2*'[6]DV-CAGR'!AF89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.6520870108369328</v>
       </c>
       <c r="AD2" s="66">
-        <f>AC2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>2.0380537429991765</v>
+        <f>$B$2*'[6]DV-CAGR'!AG89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.676238381608671</v>
       </c>
       <c r="AE2" s="66">
-        <f>AD2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>2.0905427236633498</v>
+        <f>$B$2*'[6]DV-CAGR'!AH89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.7003897523804092</v>
       </c>
       <c r="AF2" s="66">
-        <f>AE2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>2.1443835298623637</v>
+        <f>$B$2*'[6]DV-CAGR'!AI89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.7245411231521475</v>
       </c>
       <c r="AG2" s="66">
-        <f>AF2*(1+'[5]DV-CAGR'!$N$82)</f>
-        <v>2.1996109771375667</v>
+        <f>$B$2*'[6]DV-CAGR'!AJ89/'[6]DV-CAGR'!$E$89</f>
+        <v>1.7486924939238857</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -25196,128 +26009,128 @@
         <v>1</v>
       </c>
       <c r="C3" s="66">
-        <f>B3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.95480526999756732</v>
+        <f>B3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.95558769253233078</v>
       </c>
       <c r="D3" s="66">
-        <f>C3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.91165310361512741</v>
+        <f>C3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.91314783811926437</v>
       </c>
       <c r="E3" s="66">
-        <f>D3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.87045118774136199</v>
+        <f>D3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.87259283556927414</v>
       </c>
       <c r="F3" s="66">
-        <f>E3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.8311113813310943</v>
+        <f>E3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.83383897426188625</v>
       </c>
       <c r="G3" s="66">
-        <f>F3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.79354952684988667</v>
+        <f>F3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.79680626135844146</v>
       </c>
       <c r="H3" s="66">
-        <f>G3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.75768527024034782</v>
+        <f>G3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.76141825668682639</v>
       </c>
       <c r="I3" s="66">
-        <f>H3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.72344188902501505</v>
+        <f>H3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.72760191495935433</v>
       </c>
       <c r="J3" s="66">
-        <f>I3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.69074612817807968</v>
+        <f>I3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.69528743499811463</v>
       </c>
       <c r="K3" s="66">
-        <f>J3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.65952804341484561</v>
+        <f>J3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.66440811565657132</v>
       </c>
       <c r="L3" s="66">
-        <f>K3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.62972085156367896</v>
+        <f>K3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.63490021814001696</v>
       </c>
       <c r="M3" s="66">
-        <f>L3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.60126078770035651</v>
+        <f>L3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.60670283444069228</v>
       </c>
       <c r="N3" s="66">
-        <f>M3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.57408696873918885</v>
+        <f>M3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.5797577616160059</v>
       </c>
       <c r="O3" s="66">
-        <f>N3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.54814126318910616</v>
+        <f>N3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.55400938165034819</v>
       </c>
       <c r="P3" s="66">
-        <f>O3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.52336816679608211</v>
+        <f>O3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.52940454665251957</v>
       </c>
       <c r="Q3" s="66">
-        <f>P3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.49971468380586503</v>
+        <f>P3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.50589246915180586</v>
       </c>
       <c r="R3" s="66">
-        <f>Q3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.47713021359300795</v>
+        <f>Q3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.48342461726625746</v>
       </c>
       <c r="S3" s="66">
-        <f>R3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.45556644241366889</v>
+        <f>R3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.4619546145267881</v>
       </c>
       <c r="T3" s="66">
-        <f>S3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.43497724005061433</v>
+        <f>S3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.44143814415031579</v>
       </c>
       <c r="U3" s="66">
-        <f>T3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.41531856112932347</v>
+        <f>T3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.42183285756435468</v>
       </c>
       <c r="V3" s="66">
-        <f>U3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.39654835089408486</v>
+        <f>U3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.40309828699424105</v>
       </c>
       <c r="W3" s="66">
-        <f>V3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.37862645524251676</v>
+        <f>V3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.38519576193256205</v>
       </c>
       <c r="X3" s="66">
-        <f>W3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.36151453482605306</v>
+        <f>W3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.36808832931836999</v>
       </c>
       <c r="Y3" s="66">
-        <f>X3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.34517598303263453</v>
+        <f>X3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.35174067726142189</v>
       </c>
       <c r="Z3" s="66">
-        <f>Y3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.32957584767615034</v>
+        <f>Y3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.33611906215400139</v>
       </c>
       <c r="AA3" s="66">
-        <f>Z3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.31468075622510383</v>
+        <f>Z3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.32119123901987329</v>
       </c>
       <c r="AB3" s="66">
-        <f>AA3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.30045884441054893</v>
+        <f>AA3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.30692639495660101</v>
       </c>
       <c r="AC3" s="66">
-        <f>AB3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.28687968806057124</v>
+        <f>AB3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.29329508553384515</v>
       </c>
       <c r="AD3" s="66">
-        <f>AC3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.27391423801549158</v>
+        <f>AC3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.28026917401635965</v>
       </c>
       <c r="AE3" s="66">
-        <f>AD3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.26153475798455939</v>
+        <f>AD3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.26782177328623541</v>
       </c>
       <c r="AF3" s="66">
-        <f>AE3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.24971476521119565</v>
+        <f>AE3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.25592719034451072</v>
       </c>
       <c r="AG3" s="66">
-        <f>AF3*(1+'[5]DV-CAGR'!$N$83)</f>
-        <v>0.23842897381985478</v>
+        <f>AF3*(1+'[6]DV-CAGR'!$N$83)</f>
+        <v>0.2445608732775936</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -25328,96 +26141,127 @@
         <v>1</v>
       </c>
       <c r="C4" s="66">
+        <f>'[6]Air-Cal'!C7</f>
         <v>0.39189939646309102</v>
       </c>
       <c r="D4" s="66">
+        <f>'[6]Air-Cal'!D7</f>
         <v>0.34910898091961506</v>
       </c>
       <c r="E4" s="67">
+        <f>D4+($B$4-$D$4)/COUNT($E$1:$G$1)</f>
         <v>0.56607265394641004</v>
       </c>
       <c r="F4" s="67">
+        <f t="shared" ref="F4:G4" si="0">E4+($B$4-$D$4)/COUNT($E$1:$G$1)</f>
         <v>0.78303632697320502</v>
       </c>
       <c r="G4" s="68">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H4" s="66">
+        <f>G4*'[6]Air-CAGR'!$I$56</f>
         <v>1.042</v>
       </c>
       <c r="I4" s="66">
+        <f>H4*'[6]Air-CAGR'!$I$56</f>
         <v>1.0857640000000002</v>
       </c>
       <c r="J4" s="66">
+        <f>I4*'[6]Air-CAGR'!$I$56</f>
         <v>1.1313660880000003</v>
       </c>
       <c r="K4" s="66">
+        <f>J4*'[6]Air-CAGR'!$I$56</f>
         <v>1.1788834636960004</v>
       </c>
       <c r="L4" s="66">
+        <f>K4*'[6]Air-CAGR'!$I$56</f>
         <v>1.2283965691712324</v>
       </c>
       <c r="M4" s="66">
+        <f>L4*'[6]Air-CAGR'!$I$56</f>
         <v>1.2799892250764242</v>
       </c>
       <c r="N4" s="66">
+        <f>M4*'[6]Air-CAGR'!$I$56</f>
         <v>1.333748772529634</v>
       </c>
       <c r="O4" s="66">
+        <f>N4*'[6]Air-CAGR'!$I$56</f>
         <v>1.3897662209758785</v>
       </c>
       <c r="P4" s="66">
+        <f>O4*'[6]Air-CAGR'!$I$56</f>
         <v>1.4481364022568655</v>
       </c>
       <c r="Q4" s="66">
+        <f>P4*'[6]Air-CAGR'!$I$56</f>
         <v>1.5089581311516538</v>
       </c>
       <c r="R4" s="66">
+        <f>Q4*'[6]Air-CAGR'!$I$56</f>
         <v>1.5723343726600234</v>
       </c>
       <c r="S4" s="66">
+        <f>R4*'[6]Air-CAGR'!$I$56</f>
         <v>1.6383724163117444</v>
       </c>
       <c r="T4" s="66">
+        <f>S4*'[6]Air-CAGR'!$I$56</f>
         <v>1.7071840577968376</v>
       </c>
       <c r="U4" s="66">
+        <f>T4*'[6]Air-CAGR'!$I$56</f>
         <v>1.7788857882243048</v>
       </c>
       <c r="V4" s="66">
+        <f>U4*'[6]Air-CAGR'!$I$56</f>
         <v>1.8535989913297257</v>
       </c>
       <c r="W4" s="66">
+        <f>V4*'[6]Air-CAGR'!$I$56</f>
         <v>1.9314501489655742</v>
       </c>
       <c r="X4" s="66">
+        <f>W4*'[6]Air-CAGR'!$I$56</f>
         <v>2.0125710552221285</v>
       </c>
       <c r="Y4" s="66">
+        <f>X4*'[6]Air-CAGR'!$I$56</f>
         <v>2.0970990395414582</v>
       </c>
       <c r="Z4" s="66">
+        <f>Y4*'[6]Air-CAGR'!$I$56</f>
         <v>2.1851771992021995</v>
       </c>
       <c r="AA4" s="66">
+        <f>Z4*'[6]Air-CAGR'!$I$56</f>
         <v>2.2769546415686919</v>
       </c>
       <c r="AB4" s="66">
+        <f>AA4*'[6]Air-CAGR'!$I$56</f>
         <v>2.372586736514577</v>
       </c>
       <c r="AC4" s="66">
+        <f>AB4*'[6]Air-CAGR'!$I$56</f>
         <v>2.4722353794481893</v>
       </c>
       <c r="AD4" s="66">
+        <f>AC4*'[6]Air-CAGR'!$I$56</f>
         <v>2.5760692653850135</v>
       </c>
       <c r="AE4" s="66">
+        <f>AD4*'[6]Air-CAGR'!$I$56</f>
         <v>2.6842641745311839</v>
       </c>
       <c r="AF4" s="66">
+        <f>AE4</f>
         <v>2.6842641745311839</v>
       </c>
       <c r="AG4" s="66">
+        <f>AE4</f>
         <v>2.6842641745311839</v>
       </c>
     </row>
@@ -25429,96 +26273,127 @@
         <v>1</v>
       </c>
       <c r="C5" s="66">
+        <f>'[6]Rail-Cal'!C4</f>
         <v>0.63449793100934282</v>
       </c>
       <c r="D5" s="66">
+        <f>'[6]Rail-Cal'!D4</f>
         <v>0.63972651023832128</v>
       </c>
       <c r="E5" s="66">
+        <f>D5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.6645703969252037</v>
       </c>
       <c r="F5" s="66">
+        <f>E5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.69037910013263448</v>
       </c>
       <c r="G5" s="66">
+        <f>F5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.71719008867256129</v>
       </c>
       <c r="H5" s="66">
+        <f>G5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.74504228646454973</v>
       </c>
       <c r="I5" s="66">
+        <f>H5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.77397612904513235</v>
       </c>
       <c r="J5" s="66">
+        <f>I5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.80403362227170794</v>
       </c>
       <c r="K5" s="66">
+        <f>J5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.83525840330621659</v>
       </c>
       <c r="L5" s="66">
+        <f>K5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.86769580396712631</v>
       </c>
       <c r="M5" s="66">
+        <f>L5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.90139291654170428</v>
       </c>
       <c r="N5" s="66">
+        <f>M5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.93639866215411915</v>
       </c>
       <c r="O5" s="66">
+        <f>N5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>0.97276386178862961</v>
       </c>
       <c r="P5" s="66">
+        <f>O5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.0105413100709708</v>
       </c>
       <c r="Q5" s="66">
+        <f>P5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.0497858519150536</v>
       </c>
       <c r="R5" s="66">
+        <f>Q5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.0905544621462504</v>
       </c>
       <c r="S5" s="66">
+        <f>R5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.1329063282168657</v>
       </c>
       <c r="T5" s="66">
+        <f>S5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.1769029361338745</v>
       </c>
       <c r="U5" s="66">
+        <f>T5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.2226081597236811</v>
       </c>
       <c r="V5" s="66">
+        <f>U5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.2700883533634872</v>
       </c>
       <c r="W5" s="66">
+        <f>V5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.3194124483139007</v>
       </c>
       <c r="X5" s="66">
+        <f>W5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.3706520527926351</v>
       </c>
       <c r="Y5" s="66">
+        <f>X5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.4238815559345908</v>
       </c>
       <c r="Z5" s="66">
+        <f>Y5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.4791782357892407</v>
       </c>
       <c r="AA5" s="66">
+        <f>Z5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.5366223715121146</v>
       </c>
       <c r="AB5" s="66">
+        <f>AA5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.5962973599132575</v>
       </c>
       <c r="AC5" s="66">
+        <f>AB5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.6582898365318681</v>
       </c>
       <c r="AD5" s="66">
+        <f>AC5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.72268980141289</v>
       </c>
       <c r="AE5" s="66">
+        <f>AD5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.789590749768158</v>
       </c>
       <c r="AF5" s="66">
+        <f>AE5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.8590898077117939</v>
       </c>
       <c r="AG5" s="66">
+        <f>AF5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$4)</f>
         <v>1.9312878732669065</v>
       </c>
     </row>
@@ -25530,96 +26405,127 @@
         <v>1</v>
       </c>
       <c r="C6" s="66">
+        <f>B6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.98896712459176861</v>
       </c>
       <c r="D6" s="66">
+        <f>C6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.97805597352331075</v>
       </c>
       <c r="E6" s="66">
+        <f>D6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.96726520382515158</v>
       </c>
       <c r="F6" s="66">
+        <f>E6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.95659348734463112</v>
       </c>
       <c r="G6" s="66">
+        <f>F6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.94603951058243219</v>
       </c>
       <c r="H6" s="66">
+        <f>G6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.93560197453091198</v>
       </c>
       <c r="I6" s="66">
+        <f>H6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.92527959451421715</v>
       </c>
       <c r="J6" s="66">
+        <f>I6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.9150711000301629</v>
       </c>
       <c r="K6" s="66">
+        <f>J6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.90497523459385687</v>
       </c>
       <c r="L6" s="66">
+        <f>K6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.89499075558304786</v>
       </c>
       <c r="M6" s="66">
+        <f>L6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.88511643408518126</v>
       </c>
       <c r="N6" s="66">
+        <f>M6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.87535105474614139</v>
       </c>
       <c r="O6" s="66">
+        <f>N6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.86569341562066326</v>
       </c>
       <c r="P6" s="66">
+        <f>O6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.85614232802439416</v>
       </c>
       <c r="Q6" s="66">
+        <f>P6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.84669661638758786</v>
       </c>
       <c r="R6" s="66">
+        <f>Q6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.83735511811041252</v>
       </c>
       <c r="S6" s="66">
+        <f>R6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.82811668341985545</v>
       </c>
       <c r="T6" s="66">
+        <f>S6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.81898017522820643</v>
       </c>
       <c r="U6" s="66">
+        <f>T6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.80994446899310213</v>
       </c>
       <c r="V6" s="66">
+        <f>U6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.80100845257911513</v>
       </c>
       <c r="W6" s="66">
+        <f>V6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.79217102612086954</v>
       </c>
       <c r="X6" s="66">
+        <f>W6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.78343110188766718</v>
       </c>
       <c r="Y6" s="66">
+        <f>X6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.77478760414960712</v>
       </c>
       <c r="Z6" s="66">
+        <f>Y6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.76623946904518236</v>
       </c>
       <c r="AA6" s="66">
+        <f>Z6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.75778564445033747</v>
       </c>
       <c r="AB6" s="66">
+        <f>AA6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.7494250898489706</v>
       </c>
       <c r="AC6" s="66">
+        <f>AB6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.74115677620486431</v>
       </c>
       <c r="AD6" s="66">
+        <f>AC6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.73297968583502959</v>
       </c>
       <c r="AE6" s="66">
+        <f>AD6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.72489281228444713</v>
       </c>
       <c r="AF6" s="66">
+        <f>AE6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.71689516020219035</v>
       </c>
       <c r="AG6" s="66">
+        <f>AF6*(1+'[6]BAADTbVT_Ships-Cal psgr CAGR'!$C$66)</f>
         <v>0.70898574521891555</v>
       </c>
     </row>
@@ -25739,100 +26645,100 @@
       <c r="A1" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="8">
+      <c r="B1" s="9">
         <v>2019</v>
       </c>
-      <c r="C1" s="8">
+      <c r="C1" s="9">
         <v>2020</v>
       </c>
-      <c r="D1" s="8">
+      <c r="D1" s="9">
         <v>2021</v>
       </c>
-      <c r="E1" s="8">
+      <c r="E1" s="9">
         <v>2022</v>
       </c>
-      <c r="F1" s="8">
+      <c r="F1" s="9">
         <v>2023</v>
       </c>
-      <c r="G1" s="8">
+      <c r="G1" s="9">
         <v>2024</v>
       </c>
-      <c r="H1" s="8">
+      <c r="H1" s="9">
         <v>2025</v>
       </c>
-      <c r="I1" s="8">
+      <c r="I1" s="9">
         <v>2026</v>
       </c>
-      <c r="J1" s="8">
+      <c r="J1" s="9">
         <v>2027</v>
       </c>
-      <c r="K1" s="8">
+      <c r="K1" s="9">
         <v>2028</v>
       </c>
-      <c r="L1" s="8">
+      <c r="L1" s="9">
         <v>2029</v>
       </c>
-      <c r="M1" s="8">
+      <c r="M1" s="9">
         <v>2030</v>
       </c>
-      <c r="N1" s="8">
+      <c r="N1" s="9">
         <v>2031</v>
       </c>
-      <c r="O1" s="8">
+      <c r="O1" s="9">
         <v>2032</v>
       </c>
-      <c r="P1" s="8">
+      <c r="P1" s="9">
         <v>2033</v>
       </c>
-      <c r="Q1" s="8">
+      <c r="Q1" s="9">
         <v>2034</v>
       </c>
-      <c r="R1" s="8">
+      <c r="R1" s="9">
         <v>2035</v>
       </c>
-      <c r="S1" s="8">
+      <c r="S1" s="9">
         <v>2036</v>
       </c>
-      <c r="T1" s="8">
+      <c r="T1" s="9">
         <v>2037</v>
       </c>
-      <c r="U1" s="8">
+      <c r="U1" s="9">
         <v>2038</v>
       </c>
-      <c r="V1" s="8">
+      <c r="V1" s="9">
         <v>2039</v>
       </c>
-      <c r="W1" s="8">
+      <c r="W1" s="9">
         <v>2040</v>
       </c>
-      <c r="X1" s="8">
+      <c r="X1" s="9">
         <v>2041</v>
       </c>
-      <c r="Y1" s="8">
+      <c r="Y1" s="9">
         <v>2042</v>
       </c>
-      <c r="Z1" s="8">
+      <c r="Z1" s="9">
         <v>2043</v>
       </c>
-      <c r="AA1" s="8">
+      <c r="AA1" s="9">
         <v>2044</v>
       </c>
-      <c r="AB1" s="8">
+      <c r="AB1" s="9">
         <v>2045</v>
       </c>
-      <c r="AC1" s="8">
+      <c r="AC1" s="9">
         <v>2046</v>
       </c>
-      <c r="AD1" s="8">
+      <c r="AD1" s="9">
         <v>2047</v>
       </c>
-      <c r="AE1" s="8">
+      <c r="AE1" s="9">
         <v>2048</v>
       </c>
-      <c r="AF1" s="8">
+      <c r="AF1" s="9">
         <v>2049</v>
       </c>
-      <c r="AG1" s="8">
+      <c r="AG1" s="9">
         <v>2050</v>
       </c>
     </row>
@@ -25844,128 +26750,128 @@
         <v>1</v>
       </c>
       <c r="C2" s="66">
-        <f>B2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0042610726525127</v>
+        <f>$B$2*'[6]DV-CAGR'!F91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0035677890698831</v>
       </c>
       <c r="D2" s="66">
-        <f>C2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0085403020451755</v>
+        <f>$B$2*'[6]DV-CAGR'!G91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.007135578139766</v>
       </c>
       <c r="E2" s="66">
-        <f>D2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0128377655451772</v>
+        <f>$B$2*'[6]DV-CAGR'!H91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.010703367209649</v>
       </c>
       <c r="F2" s="66">
-        <f>E2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0171535408493739</v>
+        <f>$B$2*'[6]DV-CAGR'!I91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0142711562795321</v>
       </c>
       <c r="G2" s="66">
-        <f>F2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0214877059856937</v>
+        <f>$B$2*'[6]DV-CAGR'!J91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0178389453494152</v>
       </c>
       <c r="H2" s="66">
-        <f>G2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0258403393145474</v>
+        <f>$B$2*'[6]DV-CAGR'!K91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0214067344192981</v>
       </c>
       <c r="I2" s="66">
-        <f>H2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.030211519530245</v>
+        <f>$B$2*'[6]DV-CAGR'!L91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0249745234891812</v>
       </c>
       <c r="J2" s="66">
-        <f>I2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0346013256624189</v>
+        <f>$B$2*'[6]DV-CAGR'!M91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0285423125590643</v>
       </c>
       <c r="K2" s="66">
-        <f>J2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0390098370774525</v>
+        <f>$B$2*'[6]DV-CAGR'!N91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0321101016289473</v>
       </c>
       <c r="L2" s="66">
-        <f>K2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0434371334799151</v>
+        <f>$B$2*'[6]DV-CAGR'!O91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0356778906988302</v>
       </c>
       <c r="M2" s="66">
-        <f>L2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0478832949140027</v>
+        <f>$B$2*'[6]DV-CAGR'!P91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0392456797687133</v>
       </c>
       <c r="N2" s="66">
-        <f>M2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0523484017649856</v>
+        <f>$B$2*'[6]DV-CAGR'!Q91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0428134688385964</v>
       </c>
       <c r="O2" s="66">
-        <f>N2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0568325347606617</v>
+        <f>$B$2*'[6]DV-CAGR'!R91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0463812579084795</v>
       </c>
       <c r="P2" s="66">
-        <f>O2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0613357749728161</v>
+        <f>$B$2*'[6]DV-CAGR'!S91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0499490469783623</v>
       </c>
       <c r="Q2" s="66">
-        <f>P2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0658582038186861</v>
+        <f>$B$2*'[6]DV-CAGR'!T91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0535168360482454</v>
       </c>
       <c r="R2" s="66">
-        <f>Q2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0703999030624343</v>
+        <f>$B$2*'[6]DV-CAGR'!U91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0570846251181285</v>
       </c>
       <c r="S2" s="66">
-        <f>R2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0749609548166259</v>
+        <f>$B$2*'[6]DV-CAGR'!V91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0606524141880116</v>
       </c>
       <c r="T2" s="66">
-        <f>S2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0795414415437141</v>
+        <f>$B$2*'[6]DV-CAGR'!W91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0642202032578945</v>
       </c>
       <c r="U2" s="66">
-        <f>T2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0841414460575303</v>
+        <f>$B$2*'[6]DV-CAGR'!X91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0677879923277775</v>
       </c>
       <c r="V2" s="66">
-        <f>U2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0887610515247816</v>
+        <f>$B$2*'[6]DV-CAGR'!Y91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0713557813976606</v>
       </c>
       <c r="W2" s="66">
-        <f>V2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.093400341466555</v>
+        <f>$B$2*'[6]DV-CAGR'!Z91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0749235704675437</v>
       </c>
       <c r="X2" s="66">
-        <f>W2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.0980593997598262</v>
+        <f>$B$2*'[6]DV-CAGR'!AA91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0784913595374266</v>
       </c>
       <c r="Y2" s="66">
-        <f>X2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1027383106389774</v>
+        <f>$B$2*'[6]DV-CAGR'!AB91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0820591486073097</v>
       </c>
       <c r="Z2" s="66">
-        <f>Y2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1074371586973193</v>
+        <f>$B$2*'[6]DV-CAGR'!AC91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0856269376771928</v>
       </c>
       <c r="AA2" s="66">
-        <f>Z2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1121560288886208</v>
+        <f>$B$2*'[6]DV-CAGR'!AD91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0891947267470758</v>
       </c>
       <c r="AB2" s="66">
-        <f>AA2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1168950065286452</v>
+        <f>$B$2*'[6]DV-CAGR'!AE91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0927625158169587</v>
       </c>
       <c r="AC2" s="66">
-        <f>AB2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1216541772966924</v>
+        <f>$B$2*'[6]DV-CAGR'!AF91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0963303048868418</v>
       </c>
       <c r="AD2" s="66">
-        <f>AC2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.126433627237148</v>
+        <f>$B$2*'[6]DV-CAGR'!AG91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.0998980939567249</v>
       </c>
       <c r="AE2" s="66">
-        <f>AD2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1312334427610389</v>
+        <f>$B$2*'[6]DV-CAGR'!AH91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.103465883026608</v>
       </c>
       <c r="AF2" s="66">
-        <f>AE2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1360537106475959</v>
+        <f>$B$2*'[6]DV-CAGR'!AI91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.1070336720964908</v>
       </c>
       <c r="AG2" s="66">
-        <f>AF2*(1+'[5]DV-CAGR'!$N$84)</f>
-        <v>1.1408945180458219</v>
+        <f>$B$2*'[6]DV-CAGR'!AJ91/'[6]DV-CAGR'!$E$91</f>
+        <v>1.1106014611663739</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -25976,128 +26882,128 @@
         <v>1</v>
       </c>
       <c r="C3" s="66">
-        <f>B3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.0238834681230935</v>
+        <f>$B$3*'[6]DV-CAGR'!F92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.0216746342172385</v>
       </c>
       <c r="D3" s="66">
-        <f>C3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.0483373562957738</v>
+        <f>$B$3*'[6]DV-CAGR'!G92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.043349268434477</v>
       </c>
       <c r="E3" s="66">
-        <f>D3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.0733752881271121</v>
+        <f>$B$3*'[6]DV-CAGR'!H92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.0650239026517156</v>
       </c>
       <c r="F3" s="66">
-        <f>E3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.0990112126052123</v>
+        <f>$B$3*'[6]DV-CAGR'!I92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.0866985368689541</v>
       </c>
       <c r="G3" s="66">
-        <f>F3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.1252594118683912</v>
+        <f>$B$3*'[6]DV-CAGR'!J92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.1083731710861926</v>
       </c>
       <c r="H3" s="66">
-        <f>G3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.1521345091619608</v>
+        <f>$B$3*'[6]DV-CAGR'!K92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.1300478053034311</v>
       </c>
       <c r="I3" s="66">
-        <f>H3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.1796514769850466</v>
+        <f>$B$3*'[6]DV-CAGR'!L92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.1517224395206695</v>
       </c>
       <c r="J3" s="66">
-        <f>I3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.2078256454319791</v>
+        <f>$B$3*'[6]DV-CAGR'!M92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.173397073737908</v>
       </c>
       <c r="K3" s="66">
-        <f>J3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.2366727107329085</v>
+        <f>$B$3*'[6]DV-CAGR'!N92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.1950717079551465</v>
       </c>
       <c r="L3" s="66">
-        <f>K3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.2662087439983976</v>
+        <f>$B$3*'[6]DV-CAGR'!O92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.2167463421723852</v>
       </c>
       <c r="M3" s="66">
-        <f>L3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.2964502001728655</v>
+        <f>$B$3*'[6]DV-CAGR'!P92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.2384209763896237</v>
       </c>
       <c r="N3" s="66">
-        <f>M3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.3274139272018723</v>
+        <f>$B$3*'[6]DV-CAGR'!Q92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.2600956106068621</v>
       </c>
       <c r="O3" s="66">
-        <f>N3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.3591171754183486</v>
+        <f>$B$3*'[6]DV-CAGR'!R92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.2817702448241006</v>
       </c>
       <c r="P3" s="66">
-        <f>O3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.3915776071530017</v>
+        <f>$B$3*'[6]DV-CAGR'!S92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.3034448790413391</v>
       </c>
       <c r="Q3" s="66">
-        <f>P3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.4248133065742512</v>
+        <f>$B$3*'[6]DV-CAGR'!T92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.3251195132585778</v>
       </c>
       <c r="R3" s="66">
-        <f>Q3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.4588427897631768</v>
+        <f>$B$3*'[6]DV-CAGR'!U92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.3467941474758163</v>
       </c>
       <c r="S3" s="66">
-        <f>R3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.4936850150290903</v>
+        <f>$B$3*'[6]DV-CAGR'!V92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.3684687816930547</v>
       </c>
       <c r="T3" s="66">
-        <f>S3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.52935939347148</v>
+        <f>$B$3*'[6]DV-CAGR'!W92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.3901434159102932</v>
       </c>
       <c r="U3" s="66">
-        <f>T3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.5658857997942097</v>
+        <f>$B$3*'[6]DV-CAGR'!X92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.4118180501275317</v>
       </c>
       <c r="V3" s="66">
-        <f>U3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.6032845833779994</v>
+        <f>$B$3*'[6]DV-CAGR'!Y92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.4334926843447704</v>
       </c>
       <c r="W3" s="66">
-        <f>V3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.6415765796173551</v>
+        <f>$B$3*'[6]DV-CAGR'!Z92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.4551673185620089</v>
       </c>
       <c r="X3" s="66">
-        <f>W3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.6807831215282631</v>
+        <f>$B$3*'[6]DV-CAGR'!AA92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.4768419527792473</v>
       </c>
       <c r="Y3" s="66">
-        <f>X3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.7209260516331171</v>
+        <f>$B$3*'[6]DV-CAGR'!AB92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.4985165869964858</v>
       </c>
       <c r="Z3" s="66">
-        <f>Y3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.7620277341294979</v>
+        <f>$B$3*'[6]DV-CAGR'!AC92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.5201912212137243</v>
       </c>
       <c r="AA3" s="66">
-        <f>Z3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.8041110673495864</v>
+        <f>$B$3*'[6]DV-CAGR'!AD92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.541865855430963</v>
       </c>
       <c r="AB3" s="66">
-        <f>AA3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.8471994965171503</v>
+        <f>$B$3*'[6]DV-CAGR'!AE92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.5635404896482015</v>
       </c>
       <c r="AC3" s="66">
-        <f>AB3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.8913170268092121</v>
+        <f>$B$3*'[6]DV-CAGR'!AF92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.5852151238654399</v>
       </c>
       <c r="AD3" s="66">
-        <f>AC3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.9364882367296739</v>
+        <f>$B$3*'[6]DV-CAGR'!AG92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.6068897580826784</v>
       </c>
       <c r="AE3" s="66">
-        <f>AD3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>1.9827382918023526</v>
+        <f>$B$3*'[6]DV-CAGR'!AH92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.6285643922999171</v>
       </c>
       <c r="AF3" s="66">
-        <f>AE3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>2.0300929585910508</v>
+        <f>$B$3*'[6]DV-CAGR'!AI92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.6502390265171556</v>
       </c>
       <c r="AG3" s="66">
-        <f>AF3*(1+'[5]DV-CAGR'!$N$85)</f>
-        <v>2.0785786190544768</v>
+        <f>$B$3*'[6]DV-CAGR'!AJ92/'[6]DV-CAGR'!$E$92</f>
+        <v>1.6719136607343941</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -26108,96 +27014,127 @@
         <v>1</v>
       </c>
       <c r="C4" s="66">
+        <f>'[6]Air-Cal'!C8</f>
         <v>0.80494672770980769</v>
       </c>
       <c r="D4" s="66">
+        <f>'[6]Air-Cal'!D8</f>
         <v>0.88189763966989509</v>
       </c>
-      <c r="E4" s="67">
+      <c r="E4" s="66">
+        <f>D4*'[6]Air-CAGR'!$J$56</f>
         <v>0.90659077358065221</v>
       </c>
-      <c r="F4" s="67">
+      <c r="F4" s="66">
+        <f>E4*'[6]Air-CAGR'!$J$56</f>
         <v>0.93197531524091048</v>
       </c>
-      <c r="G4" s="68">
+      <c r="G4" s="66">
+        <f>F4*'[6]Air-CAGR'!$J$56</f>
         <v>0.95807062406765597</v>
       </c>
       <c r="H4" s="66">
+        <f>G4*'[6]Air-CAGR'!$J$56</f>
         <v>0.98489660154155034</v>
       </c>
       <c r="I4" s="66">
+        <f>H4*'[6]Air-CAGR'!$J$56</f>
         <v>1.0124737063847138</v>
       </c>
       <c r="J4" s="66">
+        <f>I4*'[6]Air-CAGR'!$J$56</f>
         <v>1.0408229701634859</v>
       </c>
       <c r="K4" s="66">
+        <f>J4*'[6]Air-CAGR'!$J$56</f>
         <v>1.0699660133280635</v>
       </c>
       <c r="L4" s="66">
+        <f>K4*'[6]Air-CAGR'!$J$56</f>
         <v>1.0999250617012493</v>
       </c>
       <c r="M4" s="66">
+        <f>L4*'[6]Air-CAGR'!$J$56</f>
         <v>1.1307229634288842</v>
       </c>
       <c r="N4" s="66">
+        <f>M4*'[6]Air-CAGR'!$J$56</f>
         <v>1.1623832064048931</v>
       </c>
       <c r="O4" s="66">
+        <f>N4*'[6]Air-CAGR'!$J$56</f>
         <v>1.1949299361842303</v>
       </c>
       <c r="P4" s="66">
+        <f>O4*'[6]Air-CAGR'!$J$56</f>
         <v>1.2283879743973887</v>
       </c>
       <c r="Q4" s="66">
+        <f>P4*'[6]Air-CAGR'!$J$56</f>
         <v>1.2627828376805157</v>
       </c>
       <c r="R4" s="66">
+        <f>Q4*'[6]Air-CAGR'!$J$56</f>
         <v>1.2981407571355701</v>
       </c>
       <c r="S4" s="66">
+        <f>R4*'[6]Air-CAGR'!$J$56</f>
         <v>1.3344886983353661</v>
       </c>
       <c r="T4" s="66">
+        <f>S4*'[6]Air-CAGR'!$J$56</f>
         <v>1.3718543818887563</v>
       </c>
       <c r="U4" s="66">
+        <f>T4*'[6]Air-CAGR'!$J$56</f>
         <v>1.4102663045816415</v>
       </c>
       <c r="V4" s="66">
+        <f>U4*'[6]Air-CAGR'!$J$56</f>
         <v>1.4497537611099274</v>
       </c>
       <c r="W4" s="66">
+        <f>V4*'[6]Air-CAGR'!$J$56</f>
         <v>1.4903468664210053</v>
       </c>
       <c r="X4" s="66">
+        <f>W4*'[6]Air-CAGR'!$J$56</f>
         <v>1.5320765786807935</v>
       </c>
       <c r="Y4" s="66">
+        <f>X4*'[6]Air-CAGR'!$J$56</f>
         <v>1.5749747228838558</v>
       </c>
       <c r="Z4" s="66">
+        <f>Y4*'[6]Air-CAGR'!$J$56</f>
         <v>1.6190740151246037</v>
       </c>
       <c r="AA4" s="66">
+        <f>Z4*'[6]Air-CAGR'!$J$56</f>
         <v>1.6644080875480927</v>
       </c>
       <c r="AB4" s="66">
+        <f>AA4*'[6]Air-CAGR'!$J$56</f>
         <v>1.7110115139994393</v>
       </c>
       <c r="AC4" s="66">
+        <f>AB4*'[6]Air-CAGR'!$J$56</f>
         <v>1.7589198363914236</v>
       </c>
       <c r="AD4" s="66">
+        <f>AC4*'[6]Air-CAGR'!$J$56</f>
         <v>1.8081695918103835</v>
       </c>
       <c r="AE4" s="66">
+        <f>AD4*'[6]Air-CAGR'!$J$56</f>
         <v>1.8587983403810744</v>
       </c>
       <c r="AF4" s="66">
+        <f>AE4</f>
         <v>1.8587983403810744</v>
       </c>
       <c r="AG4" s="66">
+        <f>AE4</f>
         <v>1.8587983403810744</v>
       </c>
     </row>
@@ -26209,96 +27146,127 @@
         <v>1</v>
       </c>
       <c r="C5" s="66">
+        <f>'[6]Rail-Cal'!C16</f>
         <v>0.95914986038640171</v>
       </c>
       <c r="D5" s="66">
+        <f>'[6]Rail-Cal'!D16</f>
         <v>0.91453366351748455</v>
       </c>
       <c r="E5" s="66">
+        <f>D5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.88393102617206043</v>
       </c>
       <c r="F5" s="66">
+        <f>E5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.85435243140686623</v>
       </c>
       <c r="G5" s="66">
+        <f>F5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.82576361213588945</v>
       </c>
       <c r="H5" s="66">
+        <f>G5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.79813144793753033</v>
       </c>
       <c r="I5" s="66">
+        <f>H5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.77142392668427517</v>
       </c>
       <c r="J5" s="66">
+        <f>I5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.74561010745633971</v>
       </c>
       <c r="K5" s="66">
+        <f>J5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.72066008469631604</v>
       </c>
       <c r="L5" s="66">
+        <f>K5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.69654495356329749</v>
       </c>
       <c r="M5" s="66">
+        <f>L5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.67323677644634294</v>
       </c>
       <c r="N5" s="66">
+        <f>M5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.65070855059848609</v>
       </c>
       <c r="O5" s="66">
+        <f>N5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.62893417685379416</v>
       </c>
       <c r="P5" s="66">
+        <f>O5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.60788842939123344</v>
       </c>
       <c r="Q5" s="66">
+        <f>P5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.58754692651031326</v>
       </c>
       <c r="R5" s="66">
+        <f>Q5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.56788610238465231</v>
       </c>
       <c r="S5" s="66">
+        <f>R5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.54888317976074208</v>
       </c>
       <c r="T5" s="66">
+        <f>S5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.53051614357028032</v>
       </c>
       <c r="U5" s="66">
+        <f>T5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.51276371542550292</v>
       </c>
       <c r="V5" s="66">
+        <f>U5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.49560532896796722</v>
       </c>
       <c r="W5" s="66">
+        <f>V5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.47902110604222869</v>
       </c>
       <c r="X5" s="66">
+        <f>W5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.46299183366680674</v>
       </c>
       <c r="Y5" s="66">
+        <f>X5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.44749894177576122</v>
       </c>
       <c r="Z5" s="66">
+        <f>Y5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.43252448170509283</v>
       </c>
       <c r="AA5" s="66">
+        <f>Z5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.4180511053990435</v>
       </c>
       <c r="AB5" s="66">
+        <f>AA5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.40406204531220724</v>
       </c>
       <c r="AC5" s="66">
+        <f>AB5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.39054109498416784</v>
       </c>
       <c r="AD5" s="66">
+        <f>AC5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.37747259026415891</v>
       </c>
       <c r="AE5" s="66">
+        <f>AD5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.36484139116399472</v>
       </c>
       <c r="AF5" s="66">
+        <f>AE5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.35263286431824864</v>
       </c>
       <c r="AG5" s="66">
+        <f>AF5*(1+'[6]BAADTbVT_Rail-CAGR'!$K$6)</f>
         <v>0.34083286603135871</v>
       </c>
     </row>
@@ -26310,96 +27278,127 @@
         <v>1</v>
       </c>
       <c r="C6" s="66">
+        <f>B6*(1+'[6]Ships-freight CAGR'!$C$43)</f>
         <v>0.91534842984659492</v>
       </c>
       <c r="D6" s="66">
+        <f>C6*(1+'[6]Ships-freight CAGR'!$D$43)</f>
         <v>0.95750723845510444</v>
       </c>
       <c r="E6" s="66">
+        <f>D6*(1+'[6]Ships-freight CAGR'!$D$43)</f>
         <v>1.0016077832214909</v>
       </c>
       <c r="F6" s="66">
+        <f>E6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0076174299208198</v>
       </c>
       <c r="G6" s="66">
+        <f>F6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0136631345003448</v>
       </c>
       <c r="H6" s="66">
+        <f>G6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.019745113307347</v>
       </c>
       <c r="I6" s="66">
+        <f>H6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.025863583987191</v>
       </c>
       <c r="J6" s="66">
+        <f>I6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0320187654911142</v>
       </c>
       <c r="K6" s="66">
+        <f>J6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0382108780840609</v>
       </c>
       <c r="L6" s="66">
+        <f>K6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0444401433525652</v>
       </c>
       <c r="M6" s="66">
+        <f>L6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0507067842126805</v>
       </c>
       <c r="N6" s="66">
+        <f>M6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0570110249179565</v>
       </c>
       <c r="O6" s="66">
+        <f>N6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0633530910674642</v>
       </c>
       <c r="P6" s="66">
+        <f>O6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.069733209613869</v>
       </c>
       <c r="Q6" s="66">
+        <f>P6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0761516088715521</v>
       </c>
       <c r="R6" s="66">
+        <f>Q6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0826085185247816</v>
       </c>
       <c r="S6" s="66">
+        <f>R6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0891041696359303</v>
       </c>
       <c r="T6" s="66">
+        <f>S6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.0956387946537458</v>
       </c>
       <c r="U6" s="66">
+        <f>T6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1022126274216684</v>
       </c>
       <c r="V6" s="66">
+        <f>U6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1088259031861984</v>
       </c>
       <c r="W6" s="66">
+        <f>V6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1154788586053157</v>
       </c>
       <c r="X6" s="66">
+        <f>W6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1221717317569475</v>
       </c>
       <c r="Y6" s="66">
+        <f>X6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1289047621474892</v>
       </c>
       <c r="Z6" s="66">
+        <f>Y6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1356781907203741</v>
       </c>
       <c r="AA6" s="66">
+        <f>Z6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1424922598646963</v>
       </c>
       <c r="AB6" s="66">
+        <f>AA6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1493472134238845</v>
       </c>
       <c r="AC6" s="66">
+        <f>AB6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1562432967044278</v>
       </c>
       <c r="AD6" s="66">
+        <f>AC6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1631807564846544</v>
       </c>
       <c r="AE6" s="66">
+        <f>AD6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1701598410235623</v>
       </c>
       <c r="AF6" s="66">
+        <f>AE6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.1771808000697037</v>
       </c>
       <c r="AG6" s="66">
+        <f>AF6*(1+'[6]Ships-freight CAGR'!$A$50)</f>
         <v>1.184243884870122</v>
       </c>
     </row>
@@ -26407,100 +27406,131 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="66">
         <v>1</v>
       </c>
       <c r="C7" s="66">
+        <f>B7</f>
         <v>1</v>
       </c>
       <c r="D7" s="66">
+        <f t="shared" ref="D7:AG7" si="0">C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="T7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="U7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="V7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Z7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AA7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AD7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AG7" s="66">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -26520,6 +27550,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -26663,12 +27699,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AACD707-6E7B-4A78-919E-85074A00C393}">
   <ds:schemaRefs>
@@ -26678,6 +27708,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31D9DC9-F7D3-46EE-B42F-756CE28757BE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F22826-7F74-4789-B516-7D7B16062878}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26693,13 +27732,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31D9DC9-F7D3-46EE-B42F-756CE28757BE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/trans/SYFAFE/Start Year Fleet Avg Fuel Economy.xlsx
+++ b/InputData/trans/SYFAFE/Start Year Fleet Avg Fuel Economy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2026\01.EPS\01.EI\01.메일\260106_메일회신\회신파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\SYFAFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA61E30C-E895-46AB-84ED-AF8125FC6372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA75F18-7232-4B71-9BE2-DFE5E1BF454D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="784" firstSheet="1" activeTab="9" xr2:uid="{45C79576-D266-44E4-9E44-3FFC5A94C2AF}"/>
+    <workbookView xWindow="-26070" yWindow="-3450" windowWidth="28800" windowHeight="15225" tabRatio="784" firstSheet="7" activeTab="17" xr2:uid="{45C79576-D266-44E4-9E44-3FFC5A94C2AF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -1418,28 +1418,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="16">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0.0_ "/>
-    <numFmt numFmtId="181" formatCode="#,##0.000_ "/>
-    <numFmt numFmtId="182" formatCode="0.000E+00"/>
-    <numFmt numFmtId="183" formatCode="0.E+00"/>
-    <numFmt numFmtId="184" formatCode="0.0.E+00"/>
-    <numFmt numFmtId="185" formatCode="0.00.E+00"/>
-    <numFmt numFmtId="186" formatCode="0.0E+00"/>
-    <numFmt numFmtId="187" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="188" formatCode="0.0%"/>
-    <numFmt numFmtId="189" formatCode="#,##0.0"/>
-    <numFmt numFmtId="190" formatCode="0_ "/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+    <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="168" formatCode="0.0_ "/>
+    <numFmt numFmtId="169" formatCode="#,##0.000_ "/>
+    <numFmt numFmtId="170" formatCode="0.000E+00"/>
+    <numFmt numFmtId="171" formatCode="0.E+00"/>
+    <numFmt numFmtId="172" formatCode="0.0.E+00"/>
+    <numFmt numFmtId="173" formatCode="0.00.E+00"/>
+    <numFmt numFmtId="174" formatCode="0.0E+00"/>
+    <numFmt numFmtId="175" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
   <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1447,13 +1447,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1462,7 +1462,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1470,7 +1470,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1478,7 +1478,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1492,7 +1492,7 @@
     <font>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1506,7 +1506,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1515,7 +1515,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1524,21 +1524,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1584,7 +1584,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1627,7 +1627,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1642,7 +1642,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1934,10 +1934,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1992,10 +1992,10 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2012,7 +2012,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2027,7 +2027,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2035,10 +2035,10 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2047,7 +2047,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2056,7 +2056,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2065,7 +2065,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2116,7 +2116,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2131,11 +2131,11 @@
     <xf numFmtId="3" fontId="19" fillId="0" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
@@ -2161,20 +2161,20 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="12" applyFont="1" applyFill="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="13" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="13" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="13" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="13" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2183,20 +2183,20 @@
     <xf numFmtId="4" fontId="22" fillId="0" borderId="10" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="188" fontId="22" fillId="0" borderId="10" xfId="11" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="10" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="7" applyFont="1"/>
-    <xf numFmtId="41" fontId="28" fillId="14" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="28" fillId="15" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="28" fillId="15" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="28" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="28" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="28" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2205,7 +2205,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2214,19 +2214,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="13">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -2234,16 +2234,16 @@
     <cellStyle name="Font: Calibri, 9pt regular" xfId="8" xr:uid="{34523F07-E2CD-4579-9CA9-7D60CF13F706}"/>
     <cellStyle name="Footnotes: top row" xfId="13" xr:uid="{F2FEE8B8-B4DD-49F0-BF4F-351ED6A5D0FA}"/>
     <cellStyle name="Header: bottom row" xfId="9" xr:uid="{E50C72D6-644D-4D1F-8316-F11BBEF35B6F}"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="7" xr:uid="{3D0F82BB-60BE-40A2-8B19-4AEB7941BBF8}"/>
     <cellStyle name="Parent row" xfId="11" xr:uid="{A0593E00-0A26-40CB-BF73-3950DEBDC18C}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Table title" xfId="10" xr:uid="{ED917F40-A571-4790-AE56-2F27898370EE}"/>
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="쉼표 [0] 16 2 6" xfId="3" xr:uid="{CA2D334C-FB06-4B16-B2FA-D9E471462E66}"/>
     <cellStyle name="쉼표 [0] 3" xfId="4" xr:uid="{45576677-57B5-4912-9759-265B367A28F1}"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10 6" xfId="2" xr:uid="{0AB2A41D-3C67-4259-8BF2-59AA13A212EB}"/>
     <cellStyle name="표준 2" xfId="6" xr:uid="{429529D5-AA51-4644-AA00-3D3978A28F53}"/>
-    <cellStyle name="하이퍼링크" xfId="5" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2457,11 +2457,6 @@
             <v>1.404094416519162</v>
           </cell>
         </row>
-        <row r="42">
-          <cell r="H42">
-            <v>14.731070293267342</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
@@ -2480,11 +2475,6 @@
             <v>63.556825639903742</v>
           </cell>
         </row>
-        <row r="16">
-          <cell r="K16">
-            <v>155.72981935122084</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
@@ -2495,11 +2485,6 @@
         <row r="15">
           <cell r="C15">
             <v>1514.4</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="D30">
-            <v>382.85954795395736</v>
           </cell>
         </row>
       </sheetData>
@@ -2520,7 +2505,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2817,7 +2802,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4F44B24-DE0E-4ECB-B35B-2DFD270C2A7C}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -3122,16 +3107,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B546ED7-B1A4-40F1-B4C2-9D1260EDCEE9}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3306,11 +3291,11 @@
       </c>
       <c r="D6" s="35">
         <f>'SYVbT-passenger'!D6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>93.655624720642294</v>
+        <v>31619.466726938765</v>
       </c>
       <c r="E6" s="35">
         <f>'SYVbT-passenger'!E6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>63689.571035025583</v>
+        <v>21502502.152987439</v>
       </c>
       <c r="F6" s="35">
         <f>'SYVbT-passenger'!F6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
@@ -3318,7 +3303,7 @@
       </c>
       <c r="G6" s="35">
         <f>'SYVbT-passenger'!G6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
-        <v>37.462249888256913</v>
+        <v>12647.786690775505</v>
       </c>
       <c r="H6" s="35">
         <f>'SYVbT-passenger'!H6*'AVLo-passengers'!$F6 * 'BAADTbVT-Passenger'!$C6</f>
@@ -3600,11 +3585,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB42E507-73F5-4064-BAB1-9CA9B0C22CF4}">
   <dimension ref="A1:AG16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="33" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="33" width="9.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -4246,131 +4231,131 @@
       </c>
       <c r="B6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!B6</f>
-        <v>63820.688909634482</v>
+        <v>21546769.406405155</v>
       </c>
       <c r="C6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!C6</f>
-        <v>63116.563200426986</v>
+        <v>21309046.584094394</v>
       </c>
       <c r="D6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!D6</f>
-        <v>62420.206022440914</v>
+        <v>21073946.528063882</v>
       </c>
       <c r="E6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!E6</f>
-        <v>61731.531666439187</v>
+        <v>20841440.301660024</v>
       </c>
       <c r="F6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!F6</f>
-        <v>61050.455368804076</v>
+        <v>20611499.287483715</v>
       </c>
       <c r="G6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!G6</f>
-        <v>60376.893301104261</v>
+        <v>20384095.183868054</v>
       </c>
       <c r="H6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!H6</f>
-        <v>59710.762559777097</v>
+        <v>20159200.001394909</v>
       </c>
       <c r="I6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!I6</f>
-        <v>59051.981155924586</v>
+        <v>19936786.0594499</v>
       </c>
       <c r="J6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!J6</f>
-        <v>58400.468005222043</v>
+        <v>19716825.982815426</v>
       </c>
       <c r="K6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!K6</f>
-        <v>57756.142917938028</v>
+        <v>19499292.698301245</v>
       </c>
       <c r="L6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!L6</f>
-        <v>57118.926589064409</v>
+        <v>19284159.43141225</v>
       </c>
       <c r="M6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!M6</f>
-        <v>56488.740588555345</v>
+        <v>19071399.703053009</v>
       </c>
       <c r="N6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!N6</f>
-        <v>55865.507351673914</v>
+        <v>18860987.326268643</v>
       </c>
       <c r="O6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!O6</f>
-        <v>55249.15016944526</v>
+        <v>18652896.40302169</v>
       </c>
       <c r="P6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!P6</f>
-        <v>54639.593179215102</v>
+        <v>18447101.321004502</v>
       </c>
       <c r="Q6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Q6</f>
-        <v>54036.761355312374</v>
+        <v>18243576.75048684</v>
       </c>
       <c r="R6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!R6</f>
-        <v>53440.580499814874</v>
+        <v>18042297.64119821</v>
       </c>
       <c r="S6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!S6</f>
-        <v>52850.977233416859</v>
+        <v>17843239.219244644</v>
       </c>
       <c r="T6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!T6</f>
-        <v>52267.8789863973</v>
+        <v>17646376.984059449</v>
       </c>
       <c r="U6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!U6</f>
-        <v>51691.213989687865</v>
+        <v>17451686.705387641</v>
       </c>
       <c r="V6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!V6</f>
-        <v>51120.911266039409</v>
+        <v>17259144.420303613</v>
       </c>
       <c r="W6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!W6</f>
-        <v>50556.900621285946</v>
+        <v>17068726.430261731</v>
       </c>
       <c r="X6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!X6</f>
-        <v>49999.112635704965</v>
+        <v>16880409.298179466</v>
       </c>
       <c r="Y6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Y6</f>
-        <v>49447.478655473104</v>
+        <v>16694169.845552702</v>
       </c>
       <c r="Z6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!Z6</f>
-        <v>48901.930784216085</v>
+        <v>16509985.149602864</v>
       </c>
       <c r="AA6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AA6</f>
-        <v>48362.40187465187</v>
+        <v>16327832.540455546</v>
       </c>
       <c r="AB6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AB6</f>
-        <v>47828.825520326027</v>
+        <v>16147689.598350234</v>
       </c>
       <c r="AC6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AC6</f>
-        <v>47301.136047438231</v>
+        <v>15969534.150880842</v>
       </c>
       <c r="AD6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AD6</f>
-        <v>46779.268506759043</v>
+        <v>15793344.270266678</v>
       </c>
       <c r="AE6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AE6</f>
-        <v>46263.158665635769</v>
+        <v>15619098.27065352</v>
       </c>
       <c r="AF6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AF6</f>
-        <v>45752.743000086564</v>
+        <v>15446774.705444477</v>
       </c>
       <c r="AG6" s="69">
         <f>SUM(Total_CargoDistance!$B6:$H6)*BCDTRTSY_Passenger!AG6</f>
-        <v>45247.958686981779</v>
+        <v>15276352.364660289</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -5423,25 +5408,25 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6436D46A-2949-41D8-A639-3AC1063F138A}">
   <dimension ref="B1:S485"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" customWidth="1"/>
+    <col min="7" max="7" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18">
@@ -6929,31 +6914,31 @@
       <c r="B42" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C42" s="106">
+      <c r="C42" s="105">
         <f>IFERROR(Total_CargoDistance!B2/Road!C36, 0)</f>
         <v>3.4494855384074131E-4</v>
       </c>
-      <c r="D42" s="106">
+      <c r="D42" s="105">
         <f>IFERROR(Total_CargoDistance!C2/Road!D36, 0)</f>
         <v>4.537587230344271E-4</v>
       </c>
-      <c r="E42" s="106">
+      <c r="E42" s="105">
         <f>IFERROR(Total_CargoDistance!D2/Road!E36, 0)</f>
         <v>3.3955214948039873E-4</v>
       </c>
-      <c r="F42" s="106">
+      <c r="F42" s="105">
         <f>IFERROR(Total_CargoDistance!E2/Road!F36, 0)</f>
         <v>3.8835543291031518E-4</v>
       </c>
-      <c r="G42" s="106">
+      <c r="G42" s="105">
         <f>IFERROR(Total_CargoDistance!F2/Road!G36, 0)</f>
         <v>1.147549878921855E-4</v>
       </c>
-      <c r="H42" s="106">
+      <c r="H42" s="105">
         <f>IFERROR(Total_CargoDistance!G2/Road!H36, 0)</f>
         <v>4.3237660652546884E-4</v>
       </c>
-      <c r="I42" s="106">
+      <c r="I42" s="105">
         <f>IFERROR(Total_CargoDistance!H2/Road!I36, 0)</f>
         <v>1.9715881593092513E-4</v>
       </c>
@@ -6962,31 +6947,31 @@
       <c r="B43" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C43" s="106">
+      <c r="C43" s="105">
         <f>IFERROR(Total_CargoDistance!B3/Road!C37, 0)</f>
         <v>4.3725550386066337E-4</v>
       </c>
-      <c r="D43" s="106">
+      <c r="D43" s="105">
         <f>IFERROR(Total_CargoDistance!C3/Road!D37, 0)</f>
         <v>5.6725587224799282E-4</v>
       </c>
-      <c r="E43" s="106">
+      <c r="E43" s="105">
         <f>IFERROR(Total_CargoDistance!D3/Road!E37, 0)</f>
         <v>4.3041504176466358E-4</v>
       </c>
-      <c r="F43" s="106">
+      <c r="F43" s="105">
         <f>IFERROR(Total_CargoDistance!E3/Road!F37, 0)</f>
         <v>5.3012016240422985E-4</v>
       </c>
-      <c r="G43" s="106">
+      <c r="G43" s="105">
         <f>IFERROR(Total_CargoDistance!F3/Road!G37, 0)</f>
         <v>1.454629958370202E-4</v>
       </c>
-      <c r="H43" s="106">
+      <c r="H43" s="105">
         <f>IFERROR(Total_CargoDistance!G3/Road!H37, 0)</f>
         <v>5.4052551857085361E-4</v>
       </c>
-      <c r="I43" s="106">
+      <c r="I43" s="105">
         <f>IFERROR(Total_CargoDistance!H3/Road!I37, 0)</f>
         <v>2.4647349003975621E-4</v>
       </c>
@@ -12141,7 +12126,7 @@
         <v>14601</v>
       </c>
     </row>
-    <row r="481" spans="2:8" ht="17.25" thickBot="1">
+    <row r="481" spans="2:8" ht="15" thickBot="1">
       <c r="B481" s="47"/>
       <c r="C481" s="47"/>
       <c r="D481" s="47"/>
@@ -12168,7 +12153,7 @@
       </c>
       <c r="C484" s="53"/>
     </row>
-    <row r="485" spans="2:8" ht="17.25" thickBot="1">
+    <row r="485" spans="2:8" ht="15" thickBot="1">
       <c r="B485" s="54" t="s">
         <v>193</v>
       </c>
@@ -12184,15 +12169,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52A0755-1F2B-475E-8560-806C9D429711}">
   <dimension ref="A2:H19"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
@@ -12551,17 +12536,17 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6036189F-B18D-4739-955D-1003D2A7928E}">
   <dimension ref="B2:N24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
@@ -12822,7 +12807,7 @@
         <v>770665118</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="33">
+    <row r="18" spans="2:9">
       <c r="B18" s="7" t="s">
         <v>258</v>
       </c>
@@ -13015,19 +13000,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF7F156-5581-4F07-B244-400680D1D988}">
   <dimension ref="B2:I23"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="33">
+    <row r="2" spans="2:9" ht="29">
       <c r="B2" s="7" t="s">
         <v>276</v>
       </c>
@@ -13067,7 +13052,7 @@
     <row r="4" spans="2:9">
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="2:9" ht="33">
+    <row r="5" spans="2:9" ht="29">
       <c r="B5" s="7" t="s">
         <v>276</v>
       </c>
@@ -13193,7 +13178,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="49.5">
+    <row r="17" spans="2:9" ht="29">
       <c r="B17" s="7" t="s">
         <v>281</v>
       </c>
@@ -13347,16 +13332,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0CB5DA-674C-4AF4-A2E5-75DB1C804D9C}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -13399,11 +13384,11 @@
       </c>
       <c r="D2" s="35">
         <f>Total_CargoDistance!D6</f>
-        <v>93.655624720642294</v>
+        <v>31619.466726938765</v>
       </c>
       <c r="E2" s="35">
         <f>Total_CargoDistance!E6</f>
-        <v>63689.571035025583</v>
+        <v>21502502.152987439</v>
       </c>
       <c r="F2" s="35">
         <f>Total_CargoDistance!F6</f>
@@ -13411,7 +13396,7 @@
       </c>
       <c r="G2" s="35">
         <f>Total_CargoDistance!G6</f>
-        <v>37.462249888256913</v>
+        <v>12647.786690775505</v>
       </c>
       <c r="H2" s="35">
         <f>Total_CargoDistance!H6</f>
@@ -13491,11 +13476,11 @@
       </c>
       <c r="D6">
         <f>IFERROR(ships!D2/'SYFAFE-psgr'!D6, 0)</f>
-        <v>9319526.8033056203</v>
+        <v>3146404378.2411184</v>
       </c>
       <c r="E6">
         <f>IFERROR(ships!E2/'SYFAFE-psgr'!E6, 0)</f>
-        <v>6337651007.319952</v>
+        <v>2139680833379.0898</v>
       </c>
       <c r="F6">
         <f>IFERROR(ships!F2/'SYFAFE-psgr'!F6, 0)</f>
@@ -13552,11 +13537,11 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB88325F-6B94-486E-9187-0EBC1406A66C}">
   <dimension ref="A1:AI97"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="72" customWidth="1"/>
-    <col min="2" max="2" width="45.75" style="72" customWidth="1"/>
-    <col min="3" max="16384" width="8.75" style="72"/>
+    <col min="1" max="1" width="31.90625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="45.7265625" style="72" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="72"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15" customHeight="1" thickBot="1">
@@ -19881,42 +19866,42 @@
     </row>
     <row r="86" spans="1:35" ht="15" customHeight="1" thickBot="1"/>
     <row r="87" spans="1:35" ht="15" customHeight="1">
-      <c r="B87" s="105" t="s">
+      <c r="B87" s="106" t="s">
         <v>409</v>
       </c>
-      <c r="C87" s="105"/>
-      <c r="D87" s="105"/>
-      <c r="E87" s="105"/>
-      <c r="F87" s="105"/>
-      <c r="G87" s="105"/>
-      <c r="H87" s="105"/>
-      <c r="I87" s="105"/>
-      <c r="J87" s="105"/>
-      <c r="K87" s="105"/>
-      <c r="L87" s="105"/>
-      <c r="M87" s="105"/>
-      <c r="N87" s="105"/>
-      <c r="O87" s="105"/>
-      <c r="P87" s="105"/>
-      <c r="Q87" s="105"/>
-      <c r="R87" s="105"/>
-      <c r="S87" s="105"/>
-      <c r="T87" s="105"/>
-      <c r="U87" s="105"/>
-      <c r="V87" s="105"/>
-      <c r="W87" s="105"/>
-      <c r="X87" s="105"/>
-      <c r="Y87" s="105"/>
-      <c r="Z87" s="105"/>
-      <c r="AA87" s="105"/>
-      <c r="AB87" s="105"/>
-      <c r="AC87" s="105"/>
-      <c r="AD87" s="105"/>
-      <c r="AE87" s="105"/>
-      <c r="AF87" s="105"/>
-      <c r="AG87" s="105"/>
-      <c r="AH87" s="105"/>
-      <c r="AI87" s="105"/>
+      <c r="C87" s="106"/>
+      <c r="D87" s="106"/>
+      <c r="E87" s="106"/>
+      <c r="F87" s="106"/>
+      <c r="G87" s="106"/>
+      <c r="H87" s="106"/>
+      <c r="I87" s="106"/>
+      <c r="J87" s="106"/>
+      <c r="K87" s="106"/>
+      <c r="L87" s="106"/>
+      <c r="M87" s="106"/>
+      <c r="N87" s="106"/>
+      <c r="O87" s="106"/>
+      <c r="P87" s="106"/>
+      <c r="Q87" s="106"/>
+      <c r="R87" s="106"/>
+      <c r="S87" s="106"/>
+      <c r="T87" s="106"/>
+      <c r="U87" s="106"/>
+      <c r="V87" s="106"/>
+      <c r="W87" s="106"/>
+      <c r="X87" s="106"/>
+      <c r="Y87" s="106"/>
+      <c r="Z87" s="106"/>
+      <c r="AA87" s="106"/>
+      <c r="AB87" s="106"/>
+      <c r="AC87" s="106"/>
+      <c r="AD87" s="106"/>
+      <c r="AE87" s="106"/>
+      <c r="AF87" s="106"/>
+      <c r="AG87" s="106"/>
+      <c r="AH87" s="106"/>
+      <c r="AI87" s="106"/>
     </row>
     <row r="88" spans="1:35" ht="15" customHeight="1">
       <c r="B88" s="91" t="s">
@@ -19984,20 +19969,20 @@
     <tabColor rgb="FF1F497D"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="22.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="7" t="s">
         <v>223</v>
       </c>
@@ -20257,20 +20242,20 @@
     <tabColor rgb="FF1F497D"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
@@ -20500,20 +20485,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0244BA02-EC96-446A-B15C-CEFA31297BE9}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="23.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="2" customWidth="1"/>
+    <col min="6" max="8" width="23.26953125" style="2" customWidth="1"/>
     <col min="9" max="9" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="7" t="s">
         <v>196</v>
       </c>
@@ -20819,20 +20804,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E193DCD-8FDE-471C-B6D0-7DB36A9716D9}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="23.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="2" customWidth="1"/>
+    <col min="6" max="8" width="23.26953125" style="2" customWidth="1"/>
     <col min="9" max="9" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="7" t="s">
         <v>196</v>
       </c>
@@ -21051,14 +21036,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA2E945-FB81-4D0F-831D-87C54D22CEE1}">
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.75" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="49.5">
+    <row r="1" spans="1:37" ht="43.5">
       <c r="A1" s="7" t="s">
         <v>198</v>
       </c>
@@ -21176,147 +21161,111 @@
         <v>8</v>
       </c>
       <c r="B2" s="14">
-        <f>'[3]DV-psgr'!H41</f>
         <v>1.404094416519162</v>
       </c>
       <c r="C2" s="14">
-        <f>$B2</f>
         <v>1.404094416519162</v>
       </c>
       <c r="D2" s="14">
-        <f t="shared" ref="D2:AK7" si="0">$B2</f>
         <v>1.404094416519162</v>
       </c>
       <c r="E2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="F2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="G2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="H2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="I2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="J2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="K2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="L2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="M2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="N2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="O2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="P2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Q2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="R2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="S2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="T2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="U2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="V2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="W2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="X2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Y2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="Z2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AA2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AB2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AC2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AD2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AE2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AF2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AG2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AH2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AI2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AJ2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
       <c r="AK2" s="14">
-        <f t="shared" si="0"/>
         <v>1.404094416519162</v>
       </c>
     </row>
@@ -21325,147 +21274,111 @@
         <v>9</v>
       </c>
       <c r="B3" s="15">
-        <f>'[3]DV-psgr'!H42</f>
         <v>14.731070293267342</v>
       </c>
       <c r="C3" s="14">
-        <f t="shared" ref="C3:R7" si="1">$B3</f>
         <v>14.731070293267342</v>
       </c>
       <c r="D3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="E3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="F3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="G3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="I3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="J3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="K3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="L3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="M3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="N3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="O3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="P3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Q3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="R3" s="14">
-        <f t="shared" si="1"/>
         <v>14.731070293267342</v>
       </c>
       <c r="S3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="T3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="V3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="X3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Y3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="Z3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AA3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AB3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AC3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AD3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AE3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AF3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AG3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AH3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AI3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AJ3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
       <c r="AK3" s="14">
-        <f t="shared" si="0"/>
         <v>14.731070293267342</v>
       </c>
     </row>
@@ -21474,147 +21387,111 @@
         <v>10</v>
       </c>
       <c r="B4" s="15">
-        <f>[3]BAADTbVT_air!K16</f>
         <v>155.72981935122084</v>
       </c>
       <c r="C4" s="14">
-        <f t="shared" si="1"/>
         <v>155.72981935122084</v>
       </c>
       <c r="D4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="E4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="F4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="G4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="H4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="I4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="J4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="K4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="L4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="M4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="N4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="O4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="P4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Q4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="R4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="S4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="T4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="U4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="V4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="W4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="X4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Y4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="Z4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AA4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AB4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AC4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AD4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AE4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AF4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AG4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AH4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AI4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AJ4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
       <c r="AK4" s="14">
-        <f t="shared" si="0"/>
         <v>155.72981935122084</v>
       </c>
     </row>
@@ -21623,147 +21500,111 @@
         <v>11</v>
       </c>
       <c r="B5" s="15">
-        <f>[3]rail!D30</f>
         <v>382.85954795395736</v>
       </c>
       <c r="C5" s="14">
-        <f t="shared" si="1"/>
         <v>382.85954795395736</v>
       </c>
       <c r="D5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="E5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="F5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="G5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="H5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="J5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="L5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="M5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="N5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="O5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="P5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Q5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="R5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="S5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="T5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="U5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="V5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="W5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="X5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Y5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="Z5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AA5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AB5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AC5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AD5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AE5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AF5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AG5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AH5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AI5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AJ5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
       <c r="AK5" s="14">
-        <f t="shared" si="0"/>
         <v>382.85954795395736</v>
       </c>
     </row>
@@ -21772,112 +21613,112 @@
         <v>12</v>
       </c>
       <c r="B6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="C6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="D6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="E6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="F6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="G6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="H6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="I6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="J6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="K6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="L6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="M6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="N6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="O6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="P6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="Q6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="R6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="S6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="T6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="U6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="V6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="W6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="X6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="Y6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="Z6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AA6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AB6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AC6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AD6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AE6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AF6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AG6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AH6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AI6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AJ6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
       <c r="AK6" s="14">
-        <v>1</v>
+        <v>337.61417769892506</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -21888,143 +21729,108 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="14">
-        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="E7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="F7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="G7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="H7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="J7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="K7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="L7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="M7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="N7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="O7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="P7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Q7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="R7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="S7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="T7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="U7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="V7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="W7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="X7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Y7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Z7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AA7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AB7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AC7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AD7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AE7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AF7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AG7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AH7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AI7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AJ7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AK7" s="14">
-        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -22037,13 +21843,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6184AE60-6B95-42BC-AEF5-79CF1BC4ED6F}">
   <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.90625" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="49.5">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="43.5">
       <c r="A1" s="7" t="s">
         <v>199</v>
       </c>
@@ -23031,9 +22837,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F9BABF-C05C-4F32-9A42-D8796171F0D0}">
   <dimension ref="A1:AH7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:34" ht="66">
+    <row r="1" spans="1:34" ht="58">
       <c r="A1" s="7" t="s">
         <v>239</v>
       </c>
@@ -23788,9 +23594,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A42C4C-870C-4A21-9DFE-2049BC943C9E}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:33" ht="66">
+    <row r="1" spans="1:33" ht="58">
       <c r="A1" s="7" t="s">
         <v>239</v>
       </c>
@@ -24518,7 +24324,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2311641C-47D3-4723-A0EF-352F3398A8E3}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:33" ht="25.5" customHeight="1">
       <c r="A1" s="7" t="s">
@@ -25236,9 +25042,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A21B52-4F10-4B69-9230-60347A9D45BE}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:33" ht="148.5">
+    <row r="1" spans="1:33" ht="130.5">
       <c r="A1" s="7" t="s">
         <v>282</v>
       </c>
@@ -25952,21 +25758,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -26110,24 +25901,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AACD707-6E7B-4A78-919E-85074A00C393}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31D9DC9-F7D3-46EE-B42F-756CE28757BE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F22826-7F74-4789-B516-7D7B16062878}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26143,4 +25932,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31D9DC9-F7D3-46EE-B42F-756CE28757BE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AACD707-6E7B-4A78-919E-85074A00C393}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>